--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -756,45 +756,47 @@
       </c>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18.4</v>
+        <v>2.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>29.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>30.6</v>
+        <v>23.8</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n">
+        <v>851.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y4" s="3" t="n">
-        <v>76.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
@@ -810,21 +812,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n">
-        <v>26.2</v>
+        <v>31.7</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>17.4</v>
+        <v>16.9</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.8</v>
+        <v>24.3</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17.3</v>
+        <v>15.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
@@ -836,38 +844,44 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>262</v>
+        <v>14.6</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="O5" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>31.6</v>
+      </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>92.7</v>
+        <v>2</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S5" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>7.2</v>
+      </c>
       <c r="T5" s="3" t="n">
-        <v>70.2</v>
+        <v>14.4</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
+        <v>18.6</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="X5" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="Y5" s="3" t="n">
         <v>6.8</v>
       </c>
@@ -885,70 +899,69 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n">
-        <v>32.2</v>
+        <v>26.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>14.4</v>
+        <v>1.3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>20.8</v>
+        <v>1.1</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>91.2</v>
+        <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Q6" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>26.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="U6" s="3" t="n"/>
+        <v>81.2</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>61.5</v>
+      </c>
       <c r="V6" s="3" t="n">
-        <v>23.9</v>
+        <v>5.1</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>74.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>4.2</v>
@@ -967,70 +980,76 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="8" t="n">
-        <v>30.5</v>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19.9</v>
+        <v>7</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>25.2</v>
+        <v>4.6</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.6</v>
+        <v>15.2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.8</v>
+        <v>0.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>20.3</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>17.5</v>
+        <v>2.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="O7" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>31.6</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>19.5</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n">
-        <v>22.9</v>
+        <v>26.8</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>21.2</v>
+        <v>41.3</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.6</v>
+        <v>2.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>86.2</v>
+        <v>4.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="3" t="n"/>
       <c r="AA7" s="3" t="inlineStr">
@@ -1048,66 +1067,70 @@
       </c>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n">
-        <v>26.8</v>
+        <v>30.5</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>18.4</v>
+        <v>12.9</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>22.6</v>
+        <v>25.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.4</v>
+        <v>15.8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>18.9</v>
+        <v>4.4</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="P8" s="3" t="n">
-        <v>1.1</v>
+        <v>22.5</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>25.8</v>
+        <v>20.1</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S8" s="8" t="n">
-        <v>66.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>5.2</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>21.4</v>
+        <v>0.9</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>21.4</v>
+        <v>19.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>59.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="inlineStr">
@@ -1125,68 +1148,66 @@
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n">
-        <v>147.4</v>
+        <v>26.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>112.9</v>
-      </c>
-      <c r="F9" s="3" t="n"/>
+        <v>18.4</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>57.8</v>
+        <v>8.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>57.8</v>
+        <v>1.3</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.6</v>
+        <v>1.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>2.1</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>44.2</v>
+        <v>18.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>11.4</v>
+        <v>2.1</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>94.2</v>
+      </c>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>190.9</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>24.8</v>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n">
-        <v>318.6</v>
+        <v>2.2</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.8</v>
+        <v>4.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.6</v>
+        <v>1.4</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>110.8</v>
+        <v>2.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>23.6</v>
+        <v>2.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>382.2</v>
+        <v>5.2</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1203,67 +1224,69 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n">
-        <v>4.8</v>
+      <c r="D10" s="8" t="n">
+        <v>42.4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>19.6</v>
+        <v>5.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>16.2</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>591.2</v>
-      </c>
-      <c r="O10" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>52.1</v>
+      </c>
       <c r="P10" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>22.3</v>
-      </c>
+        <v>19.1</v>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n">
-        <v>24.5</v>
+        <v>6.3</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>23.8</v>
+        <v>48.8</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>26.9</v>
+        <v>19.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>16.2</v>
+        <v>38.6</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>31.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
@@ -1281,66 +1304,68 @@
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n">
-        <v>29.5</v>
+        <v>4.4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>17.9</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>23.8</v>
+        <v>43.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>81</v>
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M11" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>92.59999999999999</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>2.1</v>
+        <v>94.2</v>
       </c>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>28.4</v>
+        <v>2</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>26.7</v>
+        <v>2</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>24.8</v>
+        <v>4.2</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>25.2</v>
+        <v>2.2</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>22.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1358,66 +1383,74 @@
       </c>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n">
-        <v>89</v>
+        <v>23.5</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>18.5</v>
+        <v>1.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+577
+</t>
+        </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="N12" s="3" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>29.6</v>
+      </c>
       <c r="O12" s="3" t="n">
-        <v>90.2</v>
+        <v>0.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.1</v>
+        <v>6.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>934.8</v>
+        <v>8.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
+        <v>25.1</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="T12" s="3" t="n">
-        <v>0.1</v>
+        <v>61.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>24.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>22.9</v>
+        <v>4.8</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>26.8</v>
+        <v>25.4</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>81.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="inlineStr">
@@ -1435,66 +1468,70 @@
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n">
-        <v>26.4</v>
+        <v>29</v>
       </c>
       <c r="E13" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>19.9</v>
-      </c>
       <c r="M13" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="O13" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="P13" s="3" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>24.3</v>
+        <v>93.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>22.9</v>
+        <v>2</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>62.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="U13" s="3" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="V13" s="3" t="n">
-        <v>21.8</v>
+        <v>2.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>24.4</v>
+        <v>46.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1512,70 +1549,68 @@
       </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>18.5</v>
+        <v>1.3</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>16.5</v>
+        <v>2.7</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>18.9</v>
+        <v>6.6</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>91.2</v>
+        <v>6.8</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.2</v>
+        <v>2</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>22.4</v>
+        <v>25.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.2</v>
+        <v>2.9</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v>25.2</v>
-      </c>
+        <v>6.3</v>
+      </c>
+      <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X14" s="8" t="n">
-        <v>83.2</v>
+        <v>24.9</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="Z14" s="3" t="n"/>
       <c r="AA14" s="3" t="inlineStr">
@@ -1593,66 +1628,70 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n">
-        <v>29.9</v>
+        <v>26.8</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>22.5</v>
+        <v>2.2</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>16.5</v>
+        <v>98.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.9</v>
+        <v>1.5</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
+        <v>18.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>46.6</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>25.7</v>
+        <v>22.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" s="3" t="n"/>
+        <v>3.8</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V15" s="3" t="n">
-        <v>22.8</v>
+        <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>26.4</v>
+        <v>12.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>17.2</v>
+        <v>85.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>51.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z15" s="3" t="n"/>
       <c r="AA15" s="3" t="inlineStr">
@@ -1670,68 +1709,66 @@
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>13.6</v>
+        <v>18.4</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>116.6</v>
+        <v>2.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>13.9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>92.3</v>
+        <v>1.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>2.7</v>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
-        <v>951.3</v>
+        <v>19.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>953.2</v>
-      </c>
+        <v>24.7</v>
+      </c>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n">
-        <v>5.3</v>
+        <v>92.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.2</v>
+        <v>32.7</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>26.6</v>
+        <v>12.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>22.9</v>
+        <v>42.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>18.2</v>
+        <v>5.2</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1841.7</v>
+        <v>2.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>20.9</v>
+        <v>2.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>24.4</v>
+        <v>26.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.2</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" s="3" t="n"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1749,64 +1786,70 @@
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n">
-        <v>1.8</v>
+        <v>28.3</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>32.3</v>
+        <v>8.6</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>81.09999999999999</v>
+        <v>16.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>19.9</v>
+        <v>10.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>4.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q17" s="3" t="n"/>
+        <v>12.7</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>42.9</v>
+      </c>
       <c r="R17" s="8" t="n">
-        <v>26.6</v>
+        <v>46.6</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>26.6</v>
+        <v>5.7</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>22.9</v>
+        <v>16.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>704.3</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>8.300000000000001</v>
+        <v>2.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>85.3</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>151</v>
+        <v>0.2</v>
       </c>
       <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
@@ -1824,66 +1867,70 @@
       </c>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n">
-        <v>25.1</v>
+        <v>1.8</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18.5</v>
+        <v>24.3</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>2.3</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9.6</v>
+        <v>48.1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.6</v>
+        <v>0.2</v>
       </c>
       <c r="I18" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>492.1</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="n">
-        <v>21.5</v>
+        <v>4.1</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>24.8</v>
+        <v>14.6</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>82.2</v>
+        <v>48.3</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="inlineStr">
@@ -1901,68 +1948,70 @@
       </c>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n">
-        <v>3</v>
+        <v>24.1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>13.8</v>
+        <v>8.5</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>12.9</v>
+        <v>9.6</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J19" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>6262.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n">
-        <v>981.2</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.8</v>
-      </c>
       <c r="W19" s="3" t="n">
-        <v>254.3</v>
+        <v>4.8</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>85.2</v>
+        <v>28.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -1980,68 +2029,70 @@
       </c>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n">
-        <v>30.5</v>
+        <v>30.9</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>12.9</v>
+        <v>2.2</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>17.6</v>
+        <v>46.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>28.3</v>
+        <v>2.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N20" s="3" t="n"/>
+        <v>85.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>91.2</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>19.9</v>
+        <v>32.4</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>19.8</v>
+        <v>2</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.2</v>
+        <v>4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>20.2</v>
+        <v>2.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>1.9</v>
+        <v>258.3</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2059,68 +2110,70 @@
       </c>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n">
-        <v>28.3</v>
+        <v>30.5</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>39.2</v>
+        <v>12.6</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>9.6</v>
+        <v>2.9</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>12.6</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>19.2</v>
+        <v>18.3</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>28</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>292.2</v>
+        <v>393.2</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92.2</v>
+        <v>927.2</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>19.2</v>
+        <v>12.8</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.9</v>
+        <v>18.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>22</v>
+        <v>25.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="U21" s="3" t="n"/>
+        <v>20.2</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>29.2</v>
+      </c>
       <c r="V21" s="3" t="n">
-        <v>19.9</v>
+        <v>2.2</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>90.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2138,70 +2191,70 @@
       </c>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n">
-        <v>29.9</v>
+        <v>38.1</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>13.9</v>
+        <v>8.9</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.2</v>
+        <v>3.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>13.9</v>
+        <v>1.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.2</v>
       </c>
       <c r="K22" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="Q22" s="3" t="n">
-        <v>28.5</v>
+        <v>2.2</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>29.9</v>
+        <v>2.2</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>26.2</v>
+        <v>42.8</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>80.2</v>
+        <v>15.3</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
@@ -2219,70 +2272,70 @@
       </c>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n">
-        <v>194.8</v>
+        <v>28.7</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10.4</v>
+        <v>18</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>119.2</v>
+        <v>2.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.9</v>
+        <v>1.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>68.8</v>
+        <v>15.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14</v>
+        <v>389.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>96.2</v>
+        <v>3.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>185.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>18.6</v>
+        <v>2.9</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.8</v>
+        <v>1393.2</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.4</v>
+        <v>26</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>4.9</v>
+        <v>41.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>119.9</v>
+        <v>1.3</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>536</v>
+        <v>25.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>37.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>102.6</v>
+        <v>12.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.4</v>
+        <v>22.9</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>427.8</v>
+        <v>230.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.7</v>
+        <v>0.8</v>
       </c>
       <c r="Z23" s="3" t="n"/>
       <c r="AA23" s="3" t="inlineStr">
@@ -2300,65 +2353,67 @@
       </c>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n">
-        <v>22.5</v>
+        <v>29.9</v>
       </c>
       <c r="E24" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>282.8</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n">
-        <v>98.8</v>
-      </c>
       <c r="M24" s="3" t="n">
-        <v>19.2</v>
+        <v>1.7</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>391.2</v>
+        <v>20</v>
       </c>
       <c r="P24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q24" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>23.5</v>
-      </c>
       <c r="X24" s="3" t="n">
-        <v>85.2</v>
+        <v>80.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
@@ -2378,71 +2433,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n">
-        <v>0.2</v>
+      <c r="D25" s="8" t="n">
+        <v>44.6</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>18.7</v>
+        <v>9.4</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>24.9</v>
+        <v>12.2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>11.1</v>
+        <v>5.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12.9</v>
+        <v>2.2</v>
       </c>
       <c r="I25" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X25" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>0.8</v>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 1
+</t>
+        </is>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2460,68 +2518,70 @@
       </c>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n">
-        <v>28.6</v>
+        <v>295.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19.2</v>
+        <v>8.1</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>23.9</v>
+        <v>2.8</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I26" s="3" t="n"/>
+        <v>16.8</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J26" s="3" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="K26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="L26" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>24</v>
-      </c>
       <c r="X26" s="3" t="n">
-        <v>80.2</v>
+        <v>8.5</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2539,68 +2599,70 @@
       </c>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n">
-        <v>23.3</v>
+        <v>29.8</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>17.4</v>
+        <v>18.7</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>22.4</v>
+        <v>4.3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.9</v>
+        <v>1.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>12.9</v>
       </c>
       <c r="I27" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="L27" s="3" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>16.2</v>
+        <v>19.1</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>10</v>
+        <v>93.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R27" s="8" t="n">
-        <v>39.3</v>
+        <v>25.8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>5.6</v>
+        <v>0.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v>34.9</v>
+        <v>6.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>22</v>
+        <v>2.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>28.2</v>
+        <v>24.5</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>53.2</v>
+        <v>6.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2618,70 +2680,70 @@
       </c>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n">
-        <v>32.7</v>
+        <v>2.3</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>24.3</v>
+        <v>2.4</v>
       </c>
       <c r="G28" s="3" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>14</v>
-      </c>
       <c r="I28" s="3" t="n">
-        <v>3.2</v>
+        <v>19.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>958.4</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>92.2</v>
+        <v>29.1</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>11.4</v>
+        <v>2.6</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>21.2</v>
+        <v>2.1</v>
       </c>
       <c r="S28" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>853.9</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="Y28" s="3" t="n">
         <v>14.5</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>2.3</v>
       </c>
       <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2699,70 +2761,70 @@
       </c>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>18.4</v>
+        <v>32.7</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>53.9</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.7</v>
+        <v>16.8</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
+        <v>35.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.2</v>
+        <v>16.8</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>651.1</v>
+        <v>682.5</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>90.2</v>
+        <v>92.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>451.6</v>
+        <v>2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="R29" s="8" t="n">
-        <v>26.4</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="W29" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>82.59999999999999</v>
+        <v>2.2</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>32.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2780,70 +2842,70 @@
       </c>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n">
-        <v>149.4</v>
+        <v>306.1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>58.8</v>
+        <v>1.2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>11.3</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>92.8</v>
+        <v>18.5</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>4.5</v>
+        <v>3908.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>91.2</v>
+        <v>2.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.1</v>
+        <v>26.4</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>26.9</v>
+        <v>12.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>922.2</v>
+        <v>322.2</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>44.2</v>
+        <v>49.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>82.8</v>
+        <v>134.6</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>20.8</v>
+        <v>1042.6</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>22.9</v>
+        <v>14.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>17.2</v>
+        <v>322.5</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>6.5</v>
+        <v>24.4</v>
       </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2861,68 +2923,70 @@
       </c>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n">
-        <v>29.7</v>
+        <v>18.4</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>13.9</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>23.9</v>
+        <v>3.1</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>19.8</v>
+        <v>58.2</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L31" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>18.5</v>
+      <c r="M31" s="8" t="n">
+        <v>751.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>19.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>4</v>
+        <v>452.6</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>39.7</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>2644.4</v>
+        <v>28.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>15.5</v>
+        <v>48.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>23.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>22.9</v>
+        <v>2.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>25.3</v>
+        <v>2.9</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>3</v>
+        <v>63.5</v>
       </c>
       <c r="Z31" s="3" t="n"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2940,66 +3004,70 @@
       </c>
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n">
-        <v>321.8</v>
+        <v>2.2</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>35.3</v>
+        <v>4.7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>14.5</v>
+        <v>2.8</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>72.5</v>
+        <v>0.9</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>91.2</v>
+      </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>28.9</v>
+        <v>26.4</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>26.8</v>
+        <v>2.6</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>35.3</v>
+        <v>3.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>20.4</v>
+        <v>23.6</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>23</v>
+        <v>2.2</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>27.4</v>
+        <v>0.9</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>80.3</v>
+        <v>84.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3016,69 +3084,71 @@
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="8" t="n">
-        <v>3932.6</v>
+      <c r="D33" s="3" t="n">
+        <v>34.3</v>
       </c>
       <c r="E33" s="3" t="n">
+        <v>484.1</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>17.9</v>
-      </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>19.8</v>
+        <v>5.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>81.8</v>
+        <v>12.5</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="O33" s="3" t="n"/>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>24.8</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>27.8</v>
+        <v>24.9</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>22.9</v>
+        <v>2.3</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>4.8</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>21.5</v>
+        <v>24.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>86.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3094,43 +3164,51 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="8" t="n">
-        <v>32.1</v>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>3.6</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>25.8</v>
+        <v>5.3</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>12.7</v>
+        <v>14.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18</v>
+        <v>1.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.2</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="8" t="n">
-        <v>81.2</v>
+        <v>0.9</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>78.2</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>928.2</v>
+        <v>1.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>24.8</v>
@@ -3139,25 +3217,25 @@
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>24.6</v>
+        <v>29.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>68.2</v>
+        <v>63.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>24.2</v>
+        <v>2.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>62.8</v>
+        <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>13.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3175,68 +3253,66 @@
       </c>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>89.40000000000001</v>
+        <v>3.2</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>25.8</v>
       </c>
       <c r="G35" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>18.2</v>
-      </c>
       <c r="I35" s="3" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M35" s="3" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="N35" s="8" t="n">
         <v>92.2</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>928.2</v>
-      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>21.8</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n">
-        <v>27.9</v>
+        <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>33.6</v>
+        <v>53.5</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.8</v>
+        <v>45.1</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>23.9</v>
+        <v>4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>22.8</v>
+        <v>6.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>11.5</v>
+        <v>13.6</v>
       </c>
       <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3252,68 +3328,76 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="n">
-        <v>23.6</v>
+        <v>30.4</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>25.8</v>
+        <v>2.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>454.2</v>
+        <v>18.2</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>91.8</v>
+        <v>2.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="n">
-        <v>8090.2</v>
-      </c>
-      <c r="O36" s="3" t="n"/>
+      <c r="N36" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U36" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="W36" s="8" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>67.59999999999999</v>
+      <c r="V36" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>58.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>37.2</v>
+        <v>0.4</v>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3331,68 +3415,70 @@
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n">
-        <v>161.5</v>
+        <v>235.6</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>392.9</v>
+        <v>18</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>126.9</v>
+        <v>25.8</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>84634.39999999999</v>
+        <v>4.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20.3</v>
+        <v>1.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.9</v>
+        <v>1.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1441.8</v>
+        <v>0.3</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>950.2</v>
-      </c>
-      <c r="O37" s="3" t="n"/>
+        <v>9450.299999999999</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>90.2</v>
+      </c>
       <c r="P37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>7.5</v>
+        <v>12.2</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>23.5</v>
+        <v>2.4</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>26.9</v>
+        <v>48.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>10.3</v>
+        <v>90.3</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>124.9</v>
+        <v>1242.1</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>22.2</v>
+        <v>1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>25.2</v>
+        <v>125.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>13.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>4.3</v>
+        <v>32.4</v>
       </c>
       <c r="Z37" s="3" t="n"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3409,38 +3495,36 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n">
-        <v>421.2</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>18.8</v>
+      <c r="D38" s="8" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>25.4</v>
+        <v>26.3</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>13.9</v>
+        <v>9.4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>17.4</v>
+        <v>81</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21.3</v>
+        <v>1.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.1</v>
+        <v>20.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>8338.4</v>
-      </c>
+        <v>85.7</v>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n">
-        <v>81.8</v>
+        <v>9</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.2</v>
@@ -3449,31 +3533,31 @@
         <v>2.6</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>11.6</v>
+        <v>25.8</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>23.5</v>
+        <v>2.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.9</v>
+        <v>26.2</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>17.9</v>
+        <v>14.1</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>24.8</v>
+        <v>48.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>21.6</v>
+        <v>2.4</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>9.9</v>
+        <v>0.4</v>
       </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3491,66 +3575,68 @@
       </c>
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="n">
-        <v>32.8</v>
+        <v>2.3</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>51.6</v>
+        <v>18.9</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>54.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>14.1</v>
+        <v>0.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.4</v>
+        <v>12.4</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>21.3</v>
+        <v>32.3</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.1</v>
+        <v>4.1</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>61.2</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="N39" s="3" t="n">
-        <v>19.8</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n"/>
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>28.6</v>
+        <v>18.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>22.6</v>
+        <v>2.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.2</v>
+        <v>6.2</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>22</v>
+        <v>20.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>72.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>194.4</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
@@ -3566,70 +3652,72 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
+      <c r="C40" s="3" t="n">
+        <v>42.2</v>
+      </c>
       <c r="D40" s="3" t="n">
-        <v>92.5</v>
+        <v>32.6</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>18.3</v>
+        <v>13.5</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>25.6</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>98.3</v>
+        <v>17</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="O40" s="3" t="n"/>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>27.8</v>
+        <v>18.2</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>27.8</v>
+        <v>4.3</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>47.8</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.6</v>
+        <v>2.9</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.9</v>
+        <v>2.9</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>12.6</v>
+        <v>14.5</v>
       </c>
       <c r="Z40" s="3" t="n"/>
       <c r="AA40" s="3" t="inlineStr">
@@ -3645,65 +3733,71 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>42.2</v>
+      </c>
       <c r="D41" s="3" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>12.8</v>
+        <v>14.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>18.5</v>
+        <v>2.9</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M41" s="3" t="n"/>
+      <c r="M41" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="N41" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="O41" s="3" t="n"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="P41" s="3" t="n">
-        <v>10.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>31.2</v>
+        <v>3.2</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.2</v>
+        <v>2.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.2</v>
+        <v>25.1</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>82.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3722,69 +3816,69 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="n">
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>18.8</v>
+        <v>19.9</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>72.8</v>
+        <v>12.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>21</v>
+        <v>2.3</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3.6</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>1.8</v>
+        <v>89</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>922.1</v>
+      <c r="N42" s="3" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>14.8</v>
+        <v>4.1</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="T42" s="3" t="n"/>
+      <c r="T42" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="U42" s="3" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>5.1</v>
+        <v>24.8</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>82.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>2.6</v>
@@ -3803,26 +3897,24 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n">
-        <v>0.5</v>
+        <v>32.4</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.5</v>
+        <v>18.8</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>12.5</v>
+        <v>25.6</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1.1</v>
+        <v>12.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3.6</v>
@@ -3830,37 +3922,57 @@
       <c r="K43" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+      <c r="L43" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+745
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+6
+</t>
+        </is>
       </c>
       <c r="T43" s="3" t="n">
-        <v>381.9</v>
+        <v>6.8</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>95.3</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>95.7</v>
+        <v>85.2</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="X43" s="8" t="n">
-        <v>27.2</v>
+        <v>3.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0.2</v>
+        <v>24.3</v>
       </c>
       <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
@@ -3877,63 +3989,78 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="8" t="n">
-        <v>29.3</v>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4262
+7
+</t>
+        </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>2</v>
+        <v>4.6</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>44.2</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>54.7</v>
+        <v>5.4</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2429
+14
+</t>
+        </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+7
+</t>
+        </is>
       </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="n">
-        <v>366.3</v>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77 777
+</t>
+        </is>
       </c>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="8" t="n">
-        <v>6.9</v>
+      <c r="P44" s="3" t="n">
+        <v>106.5</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="S44" s="8" t="n">
-        <v>121.3</v>
+        <v>41.8</v>
       </c>
       <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.8</v>
+        <v>2.4</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.2</v>
+      <c r="X44" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>5.4</v>
+        <v>50.4</v>
       </c>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
@@ -3951,28 +4078,28 @@
       </c>
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n">
-        <v>32.3</v>
+        <v>122.3</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>25.5</v>
+        <v>192.9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>13.7</v>
+        <v>3.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>2.8</v>
+        <v>69.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.1</v>
+        <v>45.5</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.5</v>
+        <v>282.8</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>18.4</v>
@@ -3980,19 +4107,25 @@
       <c r="M45" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n">
-        <v>98.3</v>
-      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="R45" s="3" t="n">
-        <v>25.7</v>
+        <v>5.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>60.2</v>
+        <v>6.2</v>
       </c>
       <c r="T45" s="3" t="n"/>
       <c r="U45" s="3" t="n">
@@ -4000,11 +4133,8 @@
       </c>
       <c r="V45" s="3" t="n"/>
       <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
+      <c r="X45" s="3" t="n">
+        <v>83.2</v>
       </c>
       <c r="Y45" s="3" t="n"/>
       <c r="Z45" s="3" t="n"/>
@@ -4021,60 +4151,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>18.7</v>
+        <v>0.3</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.1</v>
+        <v>25.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1</v>
+        <v>3.9</v>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q46" s="3" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="8" t="n">
+        <v>290.1</v>
+      </c>
       <c r="V46" s="8" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>150.1</v>
-      </c>
+      <c r="W46" s="3" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -735,15 +735,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>31.7</v>
+        <v>91.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>24.3</v>
+      <c r="F4" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14.8</v>
@@ -754,51 +754,49 @@
       <c r="I4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n">
-        <v>8.9</v>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
       <c r="N4" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="O4" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="P4" s="3" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>851.8</v>
-      </c>
       <c r="S4" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T4" s="3" t="n"/>
+        <v>29.3</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>545.2</v>
+      </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W4" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+        <v>21.5</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -812,27 +810,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>16.9</v>
+        <v>26.2</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>11.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>24.3</v>
+        <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>14.8</v>
+        <v>81.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>15.3</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
@@ -844,48 +836,50 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>18.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>13.8</v>
+        <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>2</v>
+        <v>6.6</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>7.2</v>
+        <v>21</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>14.4</v>
+        <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>18.6</v>
+        <v>6.5</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>26.2</v>
+        <v>23.9</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="Z5" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -899,74 +893,72 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>17.4</v>
+        <v>34.2</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>21.8</v>
+        <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>11.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>91.59999999999999</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2.6</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>2</v>
+        <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S6" s="8" t="n">
-        <v>7.2</v>
+        <v>24.9</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>61.5</v>
+        <v>207.4</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>24.4</v>
+        <v>21.2</v>
+      </c>
+      <c r="W6" s="8" t="n">
+        <v>51.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>86.2</v>
+        <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Z6" s="3" t="n"/>
+        <v>77.2</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>14</v>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -980,78 +972,70 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>32.2</v>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="8" t="n">
+        <v>10.5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7</v>
+        <v>19.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4.6</v>
+        <v>25.2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15.2</v>
+        <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>31.6</v>
-      </c>
+        <v>20.2</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R7" s="3" t="n"/>
+        <v>20.1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>26.8</v>
+        <v>22.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>14.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>41.3</v>
+        <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>4.8</v>
+        <v>20.6</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z7" s="3" t="n"/>
+        <v>86.2</v>
+      </c>
+      <c r="Z7" s="3" t="inlineStr"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1065,74 +1049,72 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>12.9</v>
+        <v>26.8</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>25.2</v>
+        <v>22.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>10.6</v>
+        <v>8.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.4</v>
+        <v>11.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>15.8</v>
+        <v>14.4</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4.4</v>
+        <v>18.9</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>45.8</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>22.5</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>3.5</v>
+        <v>25.8</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>5.2</v>
+        <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>81.2</v>
+        <v>66.2</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>19.8</v>
+        <v>8.4</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>94.59999999999999</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>24.6</v>
+        <v>21.4</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>86.2</v>
+        <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+        <v>7.3</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1146,70 +1128,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>26.8</v>
+        <v>147.4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>18.4</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.1</v>
+        <v>112.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8.4</v>
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.3</v>
+        <v>957.8</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1.3</v>
+        <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2.1</v>
+        <v>16.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>18.9</v>
+        <v>949.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>20.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="O9" s="3" t="n"/>
+        <v>92.59999999999999</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="n">
+        <v>1454.6</v>
+      </c>
       <c r="P9" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="R9" s="3" t="n"/>
+        <v>129.4</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>1110.9</v>
+      </c>
       <c r="S9" s="3" t="n">
-        <v>2.2</v>
+        <v>142.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>4.2</v>
+        <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1.4</v>
+        <v>1948.8</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>2.8</v>
+        <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>126.9</v>
+      </c>
+      <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+        <v>231.1</v>
+      </c>
+      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1223,72 +1205,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="8" t="n">
-        <v>42.4</v>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>12.5</v>
+        <v>17.9</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>5.8</v>
-      </c>
+        <v>11.6</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>97.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>45.8</v>
-      </c>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>52.1</v>
+        <v>91.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="R10" s="3" t="n"/>
+        <v>25.9</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="S10" s="3" t="n">
-        <v>6.3</v>
+        <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>48.8</v>
+        <v>164.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>23.6</v>
+        <v>24.8</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>282.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>38.6</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+        <v>216.2</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1302,72 +1282,70 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
+      <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="n">
-        <v>4.4</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>18.9</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>43.7</v>
+        <v>23.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="R11" s="3" t="n">
-        <v>2</v>
+        <v>23.8</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>18.8</v>
+        <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>23.8</v>
+        <v>161.2</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>6.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+        <v>181.2</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1381,78 +1359,70 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="n">
-        <v>23.5</v>
+        <v>26.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1.9</v>
+        <v>18.3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>23.8</v>
+        <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>11.6</v>
+        <v>8.9</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="n">
-        <v>8.5</v>
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>29.6</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="n">
-        <v>0.1</v>
+        <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>8.4</v>
+        <v>24.9</v>
       </c>
       <c r="R12" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>28.5</v>
-      </c>
       <c r="T12" s="3" t="n">
-        <v>61.2</v>
+        <v>161.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>24.8</v>
+        <v>0.5</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>4.8</v>
+        <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>25.4</v>
+        <v>21.8</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.3</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+        <v>194.5</v>
+      </c>
+      <c r="Z12" s="3" t="inlineStr"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1466,74 +1436,68 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="n">
-        <v>29</v>
+        <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2.4</v>
+        <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="8" t="n">
+        <v>19.9</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>2.3</v>
+        <v>10.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>93.8</v>
+        <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>62.7</v>
+        <v>46.4</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>43</v>
+        <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>81.2</v>
+        <v>20</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>185.2</v>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1547,72 +1511,72 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>923.4</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="Y14" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+        <v>51.4</v>
+      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1626,74 +1590,70 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>98.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>2.7</v>
+        <v>16.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>92.09999999999999</v>
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>91</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>12.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>46.6</v>
+        <v>26.6</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>22.8</v>
+        <v>25.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>15.2</v>
+        <v>38.2</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>2</v>
+        <v>21.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>12.4</v>
+        <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>85.8</v>
+        <v>85.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z15" s="3" t="n"/>
+        <v>10.3</v>
+      </c>
+      <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1707,70 +1667,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="n">
-        <v>29.2</v>
+        <v>140.8</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>18.4</v>
+        <v>92.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.5</v>
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14.5</v>
+        <v>0.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>13.9</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K16" s="3" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
-        <v>19.9</v>
+        <v>2.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>92.2</v>
+        <v>453.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>32.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>42.9</v>
+        <v>1182.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>5.2</v>
+        <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1</v>
+        <v>118.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>2.2</v>
+        <v>1949.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>26.8</v>
+        <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>4.2</v>
+        <v>1708.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+        <v>1151</v>
+      </c>
+      <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1784,74 +1746,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>8.6</v>
+        <v>25.9</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>89.5</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>16.6</v>
+        <v>23.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>2.9</v>
+        <v>9.6</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="N17" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Y17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z17" s="3" t="n"/>
+      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1865,74 +1819,70 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="n">
-        <v>1.8</v>
+        <v>30.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>24.3</v>
+        <v>13.8</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2.3</v>
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48.1</v>
+        <v>12.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.2</v>
+        <v>46.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>95.3</v>
+        <v>19.2</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>91.2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>12.3</v>
-      </c>
+        <v>228.8</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="n">
-        <v>25.3</v>
+        <v>2.4</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>12.4</v>
+        <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>492.1</v>
+        <v>94.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>14.6</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>48.3</v>
+        <v>85.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z18" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1946,74 +1896,66 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n">
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="8" t="n">
+        <v>950.5</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>23.7</v>
-      </c>
       <c r="G19" s="3" t="n">
-        <v>9.6</v>
+        <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1.6</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K19" s="8" t="n">
-        <v>6262.2</v>
+        <v>1.5</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>34.3</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="n">
-        <v>26.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>2</v>
+        <v>19.9</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>6.5</v>
+        <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>2.2</v>
+        <v>10.2</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>2.5</v>
+        <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>4.8</v>
+        <v>19.9</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>28.2</v>
+        <v>21.8</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2027,74 +1969,68 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="n">
-        <v>30.9</v>
+        <v>0.3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>13.8</v>
+        <v>18.9</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.2</v>
+        <v>19.6</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>46.8</v>
+        <v>48.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>32.4</v>
+        <v>26.2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2</v>
+        <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>5.2</v>
+        <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U20" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>2.8</v>
+      <c r="V20" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>258.3</v>
+        <v>22.1</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>83.2</v>
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>9.6</v>
+      </c>
+      <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2108,74 +2044,70 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>30.5</v>
+        <v>28.9</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>12.6</v>
+        <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>2.9</v>
+        <v>23.2</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>1.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>12.6</v>
+        <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>73.8</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>393.2</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>927.2</v>
-      </c>
+        <v>18.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="n">
-        <v>26.2</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>25.2</v>
+        <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>20.2</v>
+        <v>88.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>29.2</v>
+        <v>10.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>2.2</v>
+        <v>19.1</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+        <v>10.8</v>
+      </c>
+      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2189,74 +2121,72 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>38.1</v>
+        <v>29.8</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>8.9</v>
+        <v>17.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.3</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.9</v>
+        <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>2.2</v>
+        <v>28.5</v>
+      </c>
+      <c r="R22" s="8" t="n">
+        <v>39.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>18.4</v>
+        <v>956.2</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>39.9</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>42.8</v>
+        <v>22.6</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>2.9</v>
+        <v>26.8</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>15.3</v>
+        <v>80.2</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>194.7</v>
+      </c>
+      <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2270,74 +2200,68 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>28.7</v>
+        <v>1144.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>18</v>
+        <v>290.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>112.2</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>22.8</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="n">
-        <v>389.4</v>
+        <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>3.8</v>
+        <v>2464.4</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>185.1</v>
+        <v>7.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>1393.2</v>
-      </c>
+        <v>1420.9</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>26</v>
+        <v>931.6</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>41.2</v>
+        <v>1121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.3</v>
+        <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>25.2</v>
+        <v>4.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9360.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.3</v>
+        <v>1108.4</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>12.2</v>
+        <v>102.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>22.9</v>
+        <v>197.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>230.2</v>
+        <v>927.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+        <v>12.4</v>
+      </c>
+      <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2351,74 +2275,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
+      <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>3.9</v>
+        <v>28.5</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>829.8</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>282.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>98.8</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>8.5</v>
+        <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>360.5</v>
+        <v>27.6</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>13.2</v>
+        <v>728.2</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>18.4</v>
+        <v>6.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>4.6</v>
+        <v>20.5</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0.2</v>
+        <v>22.5</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>80.2</v>
+        <v>85.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z24" s="3" t="n"/>
+      <c r="Z24" s="3" t="inlineStr"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2432,77 +2348,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="8" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="E25" s="3" t="n">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>183.2</v>
-      </c>
       <c r="K25" s="3" t="n">
-        <v>96.2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>97.8</v>
-      </c>
+        <v>15.2</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>22.1</v>
+        <v>1192.2</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>2.8</v>
+        <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>34.2</v>
+        <v>11.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>16.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 1
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>23.2</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2516,74 +2427,70 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="n">
-        <v>295.1</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>8.1</v>
+        <v>29.6</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>59.2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2.8</v>
+        <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>53.2</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>26.2</v>
+        <v>91.5</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>28.2</v>
+        <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>4.6</v>
+        <v>27.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>2.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>6.8</v>
+        <v>716.2</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>24.2</v>
+        <v>5.9</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>8.5</v>
+        <v>24.5</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>0.8</v>
+      </c>
+      <c r="Z26" s="3" t="inlineStr"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2597,74 +2504,70 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>18.7</v>
+        <v>27.3</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>97.40000000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.3</v>
+        <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.1</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>12.9</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>93.8</v>
+        <v>49.4</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.3</v>
+        <v>22.9</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.1</v>
+        <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>2.9</v>
+        <v>10.9</v>
+      </c>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="8" t="n">
+        <v>21.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>6.2</v>
+        <v>24</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z27" s="3" t="n"/>
+        <v>5.6</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2678,74 +2581,72 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
+      <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>17.4</v>
+        <v>32.7</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>7.9</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>15.8</v>
+        <v>24.3</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>19.2</v>
+        <v>3.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>18</v>
+        <v>46.3</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>68.7</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="n">
-        <v>0.2</v>
+        <v>119080.9</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>2.6</v>
+        <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2.1</v>
+        <v>23.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.5</v>
+        <v>25.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>853.9</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2.9</v>
+        <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>2.2</v>
+        <v>21</v>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>62.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z28" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2759,74 +2660,72 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="3" t="n">
-        <v>32.7</v>
+        <v>30.1</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>53.9</v>
+        <v>18.4</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>16.8</v>
+        <v>11.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>91.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>16.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>89.2</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>682.5</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>92.8</v>
-      </c>
+        <v>95.8</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="n">
-        <v>2</v>
+        <v>90.2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.7</v>
+        <v>22.4</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="3" t="n">
-        <v>6.4</v>
+      <c r="S29" s="8" t="n">
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>12.4</v>
+        <v>20.8</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>39.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z29" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2840,74 +2739,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>306.1</v>
+        <v>19498.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>18.4</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.3</v>
+        <v>118.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.2</v>
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>111.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.5</v>
+        <v>31.3</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>18.5</v>
+        <v>292.7</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>3908.6</v>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>2.4</v>
+        <v>41.2</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>12.7</v>
+        <v>120.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>322.2</v>
-      </c>
+        <v>1112.3</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>49.2</v>
+        <v>153822.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>134.6</v>
+        <v>16.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1042.6</v>
+        <v>1104.2</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>14.6</v>
+        <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>322.5</v>
+        <v>312.6</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+        <v>928.4</v>
+      </c>
+      <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2921,74 +2816,68 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
+      <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="n">
-        <v>18.4</v>
+        <v>29.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3.1</v>
+        <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>58.2</v>
+        <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>10.6</v>
+        <v>2.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>751.1</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>19.4</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>452.6</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>39.7</v>
+        <v>91.2</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R31" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="T31" s="3" t="n">
-        <v>48.2</v>
+        <v>64.2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>2.9</v>
+        <v>20.8</v>
+      </c>
+      <c r="W31" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.3</v>
+        <v>17.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="Z31" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3002,74 +2891,70 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
+      <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>4.7</v>
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>418.3</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.8</v>
+        <v>8.6</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I32" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="n">
+        <v>1219.6</v>
+      </c>
+      <c r="P32" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>82.90000000000001</v>
+      <c r="Q32" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>2.6</v>
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.9</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>0.9</v>
+        <v>25.3</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+        <v>84.5</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3083,42 +2968,38 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>34.3</v>
+        <v>32.6</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>484.1</v>
+        <v>18</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.8</v>
+        <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.5</v>
+        <v>14.6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>5.6</v>
+        <v>94.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
+        <v>18.8</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>1.2</v>
+        <v>90.2</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3127,30 +3008,30 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>2.3</v>
+        <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.2</v>
+        <v>15</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>28.2</v>
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>27.4</v>
+      </c>
+      <c r="X33" s="8" t="n">
+        <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>168.8</v>
+      </c>
+      <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3164,51 +3045,39 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>3.6</v>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>5.3</v>
+        <v>19.4</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14.6</v>
+        <v>12.7</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.2</v>
+        <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>21.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.5</v>
+        <v>93.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.9</v>
+        <v>12.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>19.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="8" t="n">
+        <v>282.5</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>24.8</v>
@@ -3217,27 +3086,27 @@
         <v>20.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>29.6</v>
+        <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>63.2</v>
+        <v>98</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X34" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="X34" s="8" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+        <v>16.9</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3251,70 +3120,70 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="n">
-        <v>3.2</v>
+        <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2.4</v>
+        <v>19.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>25.8</v>
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.7</v>
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N35" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="n">
         <v>92.2</v>
       </c>
-      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R35" s="3" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="S35" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>4</v>
+        <v>19.2</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>32</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>6.8</v>
+        <v>24.2</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+        <v>13.2</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3328,78 +3197,70 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
+      <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="n">
-        <v>30.4</v>
+        <v>23.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2.9</v>
+        <v>25.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>18.2</v>
+        <v>15.6</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>51.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2.9</v>
+        <v>91.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.6</v>
+        <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>31.2</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>231.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="S36" s="8" t="n">
-        <v>97.3</v>
+        <v>23</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U36" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.9</v>
+        <v>23.9</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>58.2</v>
+        <v>27</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>85.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+        <v>11.5</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3413,74 +3274,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="n">
-        <v>235.6</v>
+        <v>1161.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>18</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>25.8</v>
+        <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>5.6</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4.5</v>
+        <v>8711</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.9</v>
+        <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1.3</v>
+        <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.5</v>
+        <v>42.2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>18.7</v>
+        <v>981.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>9450.299999999999</v>
-      </c>
+        <v>941</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>90.2</v>
+        <v>950.6</v>
       </c>
       <c r="P37" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
-      <c r="Q37" s="3" t="n">
-        <v>12.2</v>
-      </c>
       <c r="R37" s="3" t="n">
-        <v>2.4</v>
+        <v>111</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>48.8</v>
+        <v>241.3</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>90.3</v>
+        <v>100.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>1242.1</v>
+        <v>124.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>125.2</v>
+        <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>267.2</v>
+        <v>367.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>37.2</v>
+      </c>
+      <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3494,72 +3353,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="8" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>26.3</v>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>51.5</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>9.4</v>
+        <v>19.9</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>81</v>
+        <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.1</v>
+        <v>21.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n">
-        <v>9</v>
-      </c>
+        <v>94.09999999999999</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>90.2</v>
+        <v>41</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.6</v>
+        <v>91.2</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>25.8</v>
+        <v>28.6</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>2.6</v>
+        <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.2</v>
+        <v>26.9</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>85.2</v>
+        <v>14.2</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>0.8</v>
+        <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Z38" s="3" t="n"/>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3573,72 +3430,72 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n">
-        <v>2.3</v>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="8" t="n">
+        <v>32.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="G39" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>2451.6</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="K39" s="3" t="n">
-        <v>1.2</v>
+        <v>61.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O39" s="3" t="n"/>
+      <c r="M39" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="P39" s="3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>18.6</v>
+        <v>26.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>2.6</v>
+        <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6.2</v>
+        <v>1948.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>28.6</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>20.2</v>
+        <v>82</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>21.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+        <v>114.4</v>
+      </c>
+      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3652,74 +3509,72 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>42.2</v>
-      </c>
+      <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H40" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="K40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L40" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="O40" s="3" t="n"/>
+        <v>42.1</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="3" t="n">
+        <v>92.3</v>
+      </c>
       <c r="P40" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>18.2</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>47.8</v>
+        <v>39.8</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>2.9</v>
+        <v>28.6</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>2.9</v>
+        <v>25.9</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>7.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z40" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="Z40" s="3" t="inlineStr"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3733,76 +3588,72 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>32.5</v>
+      <c r="C41" s="3" t="inlineStr"/>
+      <c r="D41" s="8" t="n">
+        <v>32.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>25.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>85.59999999999999</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
+        <v>21</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5</v>
+        <v>28.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18.9</v>
+        <v>15.4</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>0.1</v>
+        <v>92.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>2.8</v>
+        <v>25</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>82</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>4</v>
+        <v>24.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>2.6</v>
+        <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3816,74 +3667,70 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n">
-        <v>31.8</v>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="8" t="n">
+        <v>122.9</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>25.4</v>
+        <v>24.6</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>102</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>7</v>
+        <v>54.4</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>62.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.3</v>
+        <v>9.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>19.3</v>
+        <v>28.8</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>0.1</v>
+        <v>266.2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>4.1</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
       <c r="R42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24.6</v>
+        <v>91.59999999999999</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>49.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>72</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>24.8</v>
+        <v>96.3</v>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v>222.1</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>60.3</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>82.2</v>
+        <v>271.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>216.7</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3897,84 +3744,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-745
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-6
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -3988,81 +3781,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-14
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X44" s="8" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4076,68 +3818,68 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="n">
-        <v>122.3</v>
+        <v>32.3</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>192.9</v>
+        <v>25.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>3.7</v>
+        <v>13.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>69.8</v>
+        <v>117.5</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>282.8</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>190.9</v>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P45" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="n">
-        <v>5.7</v>
+        <v>22.9</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T45" s="3" t="n"/>
+        <v>160.5</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="U45" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
+        <v>22.8</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>24.2</v>
+      </c>
       <c r="X45" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4151,67 +3893,38 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 191
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="8" t="n">
-        <v>290.1</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="C46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr"/>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>9885.5</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>116560.8</v>
+      </c>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -742,48 +742,50 @@
       <c r="E4" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>24.2</v>
+      <c r="F4" s="3" t="n">
+        <v>84.5</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="8" t="n">
-        <v>82.90000000000001</v>
+      <c r="J4" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12.4</v>
+        <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>32.6</v>
+        <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>29.3</v>
+        <v>2.9</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>545.2</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
@@ -812,22 +814,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>11.4</v>
+        <v>25.2</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.6</v>
+        <v>18.6</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>2.8</v>
@@ -836,46 +838,46 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>17.6</v>
+        <v>14.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>31.4</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>29.8</v>
+        <v>20.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X5" s="8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>76.2</v>
+        <v>16.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -895,39 +897,43 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E6" s="8" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>27.6</v>
+        <v>27.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="J6" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O6" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -939,16 +945,16 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>207.4</v>
-      </c>
-      <c r="U6" s="8" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W6" s="8" t="n">
-        <v>51.3</v>
+        <v>2.7</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>41.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
@@ -957,7 +963,7 @@
         <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -973,20 +979,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="8" t="n">
-        <v>10.5</v>
+      <c r="D7" s="3" t="n">
+        <v>30.5</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>17.8</v>
+      <c r="H7" s="8" t="n">
+        <v>79.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -997,16 +1003,18 @@
       <c r="K7" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20.1</v>
@@ -1015,14 +1023,12 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>22.9</v>
+        <v>24.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>81.2</v>
+      </c>
+      <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
@@ -1030,12 +1036,14 @@
         <v>20.6</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>86.2</v>
       </c>
-      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="n">
+        <v>114.8</v>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1053,11 +1061,11 @@
       <c r="D8" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>22.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>8.4</v>
@@ -1066,13 +1074,13 @@
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>14.4</v>
+        <v>1.4</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>18.9</v>
@@ -1082,15 +1090,15 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>9.1</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1102,8 +1110,8 @@
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>94.59999999999999</v>
+      <c r="V8" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1112,9 +1120,11 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1133,25 +1143,25 @@
         <v>147.4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>112.5</v>
+        <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>57.8</v>
+        <v>51.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>957.8</v>
+        <v>5.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>949.2</v>
+        <v>47.1</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>92.59999999999999</v>
@@ -1159,9 +1169,11 @@
       <c r="M9" s="3" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>100.1</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>1454.6</v>
+        <v>451.6</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1170,26 +1182,28 @@
         <v>129.4</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1110.9</v>
+        <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>142.5</v>
+        <v>126</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1948.8</v>
+        <v>48</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>123.8</v>
+        <v>129.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="X9" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>231.1</v>
+        <v>31.4</v>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1210,34 +1224,38 @@
         <v>29.5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>23.8</v>
+        <v>2.3</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+        <v>19.6</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>97.2</v>
+      <c r="J10" s="8" t="n">
+        <v>860.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="O10" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>25.9</v>
@@ -1249,25 +1267,25 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>164.2</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W10" s="8" t="n">
-        <v>282.2</v>
+      <c r="W10" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>216.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>16.8</v>
+        <v>6.9</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1287,63 +1305,67 @@
         <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G11" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
+        <v>13.6</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K11" s="3" t="n">
-        <v>48.3</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>9.300000000000001</v>
+      <c r="M11" s="8" t="n">
+        <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>21.6</v>
+      </c>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>23.8</v>
+        <v>28.4</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>39.8</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>26.7</v>
+        <v>65.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>161.2</v>
+        <v>61.2</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
+        <v>14.8</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>26.8</v>
+        <v>22.7</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>181.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1359,56 +1381,62 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D12" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.9</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.5</v>
+        <v>81.5</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L12" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="8" t="n">
+        <v>22.6</v>
+      </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.9</v>
+        <v>2.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>161.2</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
@@ -1420,9 +1448,11 @@
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>194.5</v>
-      </c>
-      <c r="Z12" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>164.5</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1441,40 +1471,46 @@
         <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>22.7</v>
+        <v>2.2</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.9</v>
+        <v>8.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
+        <v>12.6</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="L13" s="8" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>15.8</v>
+        <v>25.3</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>46.4</v>
+        <v>20.4</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>22.9</v>
@@ -1483,7 +1519,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1491,13 +1527,15 @@
       <c r="W13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>185.2</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>85.2</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1511,7 +1549,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="n">
+        <v>133.1</v>
+      </c>
       <c r="D14" s="3" t="n">
         <v>29.9</v>
       </c>
@@ -1519,10 +1559,10 @@
         <v>18.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>49.5</v>
+        <v>14.2</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>16.5</v>
@@ -1534,38 +1574,40 @@
         <v>20.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>341.4</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="O14" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q14" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>923.4</v>
+      <c r="R14" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.8</v>
+        <v>2.5</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58.2</v>
+        <v>5.8</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>25.2</v>
+        <v>15.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>22.8</v>
@@ -1574,9 +1616,11 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>951.4</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1591,69 +1635,75 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="n">
-        <v>28.9</v>
+      <c r="D15" s="8" t="n">
+        <v>891.9</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>18.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>4.5</v>
+        <v>29.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>16.8</v>
+        <v>2.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
+        <v>11.4</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>12.1</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>91</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>25.7</v>
+        <v>4.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>38.2</v>
+        <v>58.2</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>9.5</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>85.3</v>
+        <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Z15" s="3" t="inlineStr"/>
+        <v>8.5</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1678,59 +1728,59 @@
         <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4</v>
+        <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>18.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="L16" s="3" t="n">
-        <v>2.1</v>
+        <v>951.3</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>453.2</v>
+        <v>9455.200000000001</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4.5</v>
+        <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.2</v>
+        <v>16.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1182.3</v>
+        <v>1182.9</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>118.8</v>
+        <v>21314.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1949.2</v>
+        <v>99.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>10.1</v>
+        <v>1158.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1124.6</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>1708.8</v>
-      </c>
+        <v>11274.6</v>
+      </c>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>1151</v>
+        <v>100.5</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1746,48 +1796,54 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="D17" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>89.5</v>
+        <v>28.9</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>23.3</v>
+        <v>22.3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>12.9</v>
+      <c r="H17" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>12.9</v>
+        <v>19.9</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>191.2</v>
+        <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>25.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>51.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>22.5</v>
+        <v>28.5</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>25.3</v>
+        <v>23.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>64.90000000000001</v>
@@ -1796,11 +1852,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="W17" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
       <c r="X17" s="3" t="n">
-        <v>82.2</v>
+        <v>24.8</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>2</v>
@@ -1820,11 +1878,11 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="n">
-        <v>30.2</v>
+      <c r="D18" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>24.9</v>
@@ -1833,51 +1891,53 @@
         <v>12.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>46.6</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>11</v>
+        <v>19.8</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>228.8</v>
-      </c>
-      <c r="P18" s="8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Q18" s="3" t="inlineStr"/>
+        <v>91.2</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="R18" s="3" t="n">
-        <v>2.4</v>
+        <v>23.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>94.2</v>
+        <v>54.8</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>85.2</v>
+        <v>24.3</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>1</v>
@@ -1898,7 +1958,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="8" t="n">
-        <v>950.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
@@ -1910,38 +1970,44 @@
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
+        <v>27.9</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>418.3</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P19" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>23</v>
+        <v>2.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10.2</v>
+        <v>18.8</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
@@ -1949,11 +2015,11 @@
       <c r="W19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="X19" s="8" t="n">
-        <v>21.8</v>
+      <c r="X19" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -1969,9 +2035,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="n">
-        <v>0.3</v>
+      <c r="C20" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>85.3</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>18.9</v>
@@ -1980,31 +2048,35 @@
         <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>48.6</v>
+        <v>17.6</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
+      <c r="O20" s="3" t="n">
+        <v>90.2</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>26.2</v>
+        <v>2.6</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
@@ -2013,22 +2085,22 @@
         <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>12.2</v>
+        <v>82.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>82.8</v>
+        <v>10.9</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>41.8</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
@@ -2046,19 +2118,19 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>1.3</v>
+        <v>21.2</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>17.3</v>
+        <v>1.4</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2067,45 +2139,45 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>73.8</v>
+        <v>7.8</v>
       </c>
       <c r="L21" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>13.4</v>
-      </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="n">
+        <v>92.2</v>
+      </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="R21" s="8" t="n">
-        <v>19.1</v>
+      <c r="R21" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>19.1</v>
+        <v>13.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>90.2</v>
-      </c>
+      <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2123,68 +2195,70 @@
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.2</v>
+        <v>1.7</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>15.9</v>
+        <v>1.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>91.2</v>
+        <v>99.2</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="R22" s="8" t="n">
-        <v>39.9</v>
+      <c r="R22" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>956.2</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>39.9</v>
+        <v>856.2</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>26.8</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>80.2</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>194.7</v>
+        <v>94.7</v>
       </c>
       <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
@@ -2200,63 +2274,69 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="D23" s="3" t="n">
-        <v>1144.1</v>
+        <v>1944.6</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>290.4</v>
+        <v>910.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+        <v>112.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>57.2</v>
+      </c>
       <c r="H23" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>220.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>72.5</v>
+      </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2464.4</v>
+        <v>21.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.9</v>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>931.6</v>
+        <v>931.2</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1121</v>
+        <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>4.8</v>
+        <v>11.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>9360.6</v>
+        <v>96</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1108.4</v>
+        <v>47.9</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>102.6</v>
+        <v>108.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.7</v>
+        <v>197.4</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>927.8</v>
+        <v>118.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>12.4</v>
@@ -2276,61 +2356,63 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="D24" s="8" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>829.8</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>11.4</v>
+        <v>22.8</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>58.9</v>
+      </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>98.8</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>316.4</v>
+        <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="n">
+        <v>531.2</v>
+      </c>
       <c r="P24" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>23.9</v>
+        <v>21.4</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>728.2</v>
+        <v>12.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="8" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>85.2</v>
-      </c>
+      <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
@@ -2352,8 +2434,8 @@
       <c r="D25" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="8" t="n">
-        <v>18.7</v>
+      <c r="E25" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>24.9</v>
@@ -2362,56 +2444,56 @@
         <v>11.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15.2</v>
+        <v>11.2</v>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>1192.2</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>9</v>
+        <v>15.5</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>11.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>25.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>23.2</v>
+        <v>29.9</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>69.2</v>
+        <v>67.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>9.1</v>
+        <v>59.1</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2429,10 +2511,10 @@
       </c>
       <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>59.2</v>
+        <v>28.6</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>23.9</v>
@@ -2449,31 +2531,35 @@
       <c r="J26" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K26" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>71.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>91.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>27.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.1</v>
+        <v>47.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>716.2</v>
+        <v>26.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2484,7 +2570,7 @@
       <c r="W26" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y26" s="3" t="n">
@@ -2504,11 +2590,13 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D27" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="3" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="F27" s="3" t="n">
@@ -2518,7 +2606,7 @@
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>1.5</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
@@ -2527,17 +2615,19 @@
         <v>9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+        <v>91.2</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>49.4</v>
+        <v>4.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
@@ -2546,26 +2636,26 @@
         <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="U27" s="3" t="inlineStr"/>
       <c r="V27" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
         <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2583,68 +2673,70 @@
       </c>
       <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>7.9</v>
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="H28" s="8" t="n">
+      <c r="G28" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="O28" s="3" t="n">
-        <v>119080.9</v>
+        <v>122.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>25.6</v>
+        <v>2.3</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>74</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W28" s="8" t="n">
-        <v>62.2</v>
+        <v>21.8</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>61.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.6</v>
+        <v>17.6</v>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2664,39 +2756,41 @@
       <c r="D29" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>24.3</v>
+        <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.2</v>
+        <v>1.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>91.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L29" s="8" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>40.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>22.4</v>
@@ -2711,19 +2805,19 @@
         <v>12.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>39.4</v>
+        <v>2.5</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="X29" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2739,9 +2833,11 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="D30" s="3" t="n">
-        <v>19498.4</v>
+        <v>1948.4</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>89.59999999999999</v>
@@ -2756,51 +2852,53 @@
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>31.3</v>
+        <v>4.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>292.7</v>
+        <v>12.4</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>16.4</v>
+        <v>18.6</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>41.2</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>120.7</v>
+        <v>920.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1112.3</v>
-      </c>
-      <c r="S30" s="3" t="inlineStr"/>
+        <v>112.9</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>126.4</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>153822.2</v>
+        <v>3322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.1</v>
+        <v>1088.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1104.2</v>
+        <v>1184.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>114.6</v>
+        <v>115.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.6</v>
+        <v>108.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>928.4</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2817,65 +2915,69 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="n">
-        <v>29.7</v>
+      <c r="D31" s="8" t="n">
+        <v>39.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>13.9</v>
+        <v>17.9</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>19.8</v>
+        <v>11.9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="M31" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>25.9</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>82.59999999999999</v>
+        <v>26.3</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>25.3</v>
+        <v>2.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>23.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>17.3</v>
+        <v>77.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2893,25 +2995,25 @@
       </c>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>418.3</v>
+        <v>12.8</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
@@ -2922,9 +3024,11 @@
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>1219.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -2933,25 +3037,25 @@
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>22.4</v>
+        <v>288.1</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.5</v>
+        <v>84.2</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -2968,38 +3072,44 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="D33" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>25.3</v>
+        <v>2.5</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>14.6</v>
+        <v>1.4</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>94.5</v>
+        <v>4.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>10.8</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>90.2</v>
+        <v>59.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3014,22 +3124,22 @@
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U33" s="3" t="n">
-        <v>24.2</v>
-      </c>
       <c r="V33" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="X33" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>168.8</v>
+        <v>165.8</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3045,15 +3155,17 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="8" t="n">
-        <v>92.09999999999999</v>
+      <c r="C34" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>32.1</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>41.8</v>
+      <c r="F34" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.7</v>
@@ -3062,25 +3174,31 @@
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>93.5</v>
+        <v>13.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
-      <c r="O34" s="3" t="inlineStr"/>
-      <c r="P34" s="8" t="n">
-        <v>282.5</v>
+      <c r="M34" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3089,22 +3207,22 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98</v>
+        <v>68.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="X34" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="X34" s="3" t="n">
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>16.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3122,19 +3240,19 @@
       </c>
       <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="n">
-        <v>30.4</v>
+        <v>0.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>0.8</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>18.2</v>
+        <v>10.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.9</v>
@@ -3148,10 +3266,14 @@
       <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>30.1</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>92.2</v>
+        <v>994.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3166,22 +3288,22 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>32</v>
+        <v>12.2</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.2</v>
+        <v>113.2</v>
       </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3199,7 +3321,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="n">
-        <v>23.6</v>
+        <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19</v>
@@ -3210,14 +3332,14 @@
       <c r="G36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="H36" s="8" t="n">
-        <v>51.4</v>
+      <c r="H36" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>91.8</v>
+        <v>0.5</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3226,18 +3348,20 @@
         <v>18.9</v>
       </c>
       <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>9</v>
+        <v>470.6</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q36" s="8" t="n">
-        <v>231.2</v>
+        <v>1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>31.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
@@ -3246,7 +3370,7 @@
         <v>12.6</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>28.3</v>
+        <v>2.8</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3254,11 +3378,11 @@
       <c r="W36" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>85.2</v>
+      <c r="X36" s="3" t="n">
+        <v>55.7</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3279,16 +3403,16 @@
         <v>1161.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>8711</v>
+        <v>818</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
@@ -3297,47 +3421,49 @@
         <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>42.2</v>
+        <v>49.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>981.1</v>
+        <v>28.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>941</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="O37" s="3" t="n">
         <v>950.6</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.6</v>
+        <v>120.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="V37" s="3" t="n">
         <v>111</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>241.3</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>124.8</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>116</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>367.2</v>
+        <v>3672.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>37.2</v>
+        <v>537.2</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3355,39 +3481,41 @@
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="n">
-        <v>42.1</v>
+        <v>12.3</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>51.5</v>
+        <v>524.6</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>21.3</v>
+        <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>0.1</v>
+        <v>14.4</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr"/>
+        <v>7.2</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>41</v>
+        <v>50.7</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>91.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>28.6</v>
@@ -3396,16 +3524,16 @@
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>26.9</v>
+        <v>28.9</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>274.9</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>22.2</v>
+        <v>14.9</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3414,7 +3542,7 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3431,39 +3559,39 @@
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="8" t="n">
-        <v>32.6</v>
+      <c r="D39" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>2451.6</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>79.09999999999999</v>
+        <v>10.2</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>19</v>
+        <v>68.2</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>81</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>19.8</v>
+        <v>13</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>11.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3471,17 +3599,17 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>22.6</v>
+      <c r="R39" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>1948.2</v>
+        <v>61.6</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>28.6</v>
+        <v>21.8</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>82</v>
@@ -3490,11 +3618,9 @@
         <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>114.4</v>
-      </c>
+        <v>21.6</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3511,65 +3637,67 @@
       </c>
       <c r="C40" s="3" t="inlineStr"/>
       <c r="D40" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>89</v>
+        <v>32.5</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.4</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>18.8</v>
+        <v>14.2</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="J40" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J40" s="3" t="n">
         <v>91</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="8" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="R40" s="8" t="n">
+      <c r="Q40" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>192.6</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>22.8</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>9</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>25.9</v>
+      <c r="W40" s="8" t="n">
+        <v>51.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
@@ -3590,53 +3718,53 @@
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="8" t="n">
-        <v>32.4</v>
+        <v>21.8</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>85.59999999999999</v>
+        <v>19</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>21</v>
+        <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>28.6</v>
+        <v>4.1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>15.4</v>
+        <v>10</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>4.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>92.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>82</v>
+        <v>2.4</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>24.6</v>
+        <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>91</v>
+        <v>11.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>22.8</v>
@@ -3645,10 +3773,10 @@
         <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3668,68 +3796,62 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="8" t="n">
-        <v>122.9</v>
+      <c r="D42" s="3" t="n">
+        <v>32.4</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>102</v>
+        <v>18.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>62.8</v>
+        <v>10.6</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9.9</v>
+        <v>2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>15.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="M42" s="8" t="n">
-        <v>11.9</v>
+        <v>950.2</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>29.2</v>
+        <v>11.8</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>266.2</v>
+        <v>92.2</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q42" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="R42" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v>222.1</v>
-      </c>
-      <c r="W42" s="8" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>271.2</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>216.7</v>
-      </c>
+        <v>26.5</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="3" t="inlineStr"/>
+      <c r="W42" s="3" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3744,7 +3866,9 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
@@ -3781,7 +3905,9 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
@@ -3820,64 +3946,68 @@
       </c>
       <c r="C45" s="3" t="inlineStr"/>
       <c r="D45" s="3" t="n">
-        <v>32.3</v>
+        <v>122.3</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>18.7</v>
+        <v>24.6</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>25.5</v>
+        <v>182</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>13.7</v>
+        <v>18.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>117.5</v>
+        <v>62.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>9.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>190.9</v>
-      </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
+        <v>15.6</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>19.9</v>
+        <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>22.3</v>
+        <v>89</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>92.2</v>
+        <v>266.6</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q45" s="3" t="inlineStr"/>
       <c r="R45" s="3" t="n">
-        <v>22.9</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>160.5</v>
+        <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>9.9</v>
+        <v>509.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>22.8</v>
+        <v>96.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.8</v>
+        <v>818.7</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>24.2</v>
+        <v>966.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>271.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>51.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -3893,36 +4023,66 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="n">
+        <v>22.9</v>
+      </c>
       <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="8" t="n">
-        <v>211</v>
-      </c>
-      <c r="X46" s="8" t="n">
-        <v>9885.5</v>
+      <c r="T46" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>116560.8</v>
+        <v>1211101.1</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -737,19 +737,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>91.7</v>
+        <v>31.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>84.5</v>
+        <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>15.9</v>
+        <v>15.3</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
@@ -767,10 +767,10 @@
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>21.9</v>
+        <v>8.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.9</v>
+        <v>25.2</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>45.2</v>
@@ -791,7 +791,7 @@
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.5</v>
+        <v>27.5</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
@@ -812,7 +812,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D5" s="3" t="n">
         <v>25.2</v>
       </c>
@@ -820,34 +822,34 @@
         <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.8</v>
+        <v>26.8</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>14.6</v>
+      <c r="M5" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.8</v>
+        <v>2</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
@@ -859,19 +861,19 @@
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.1</v>
+        <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>16.5</v>
+        <v>5.5</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>21.8</v>
+        <v>43.9</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>29.9</v>
@@ -897,16 +899,16 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="n">
-        <v>38.2</v>
+        <v>32.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>27.2</v>
+        <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.5</v>
+        <v>15.2</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>14.4</v>
@@ -915,25 +917,25 @@
         <v>2.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>15.4</v>
+        <v>17.4</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>97.5</v>
+        <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -945,22 +947,22 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>20.6</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.7</v>
+        <v>27.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>41.3</v>
+        <v>21.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>77.2</v>
+        <v>17.8</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1014,35 +1016,37 @@
         <v>90.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>24.2</v>
+        <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="U7" s="3" t="inlineStr"/>
+        <v>87.2</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="V7" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>114.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1057,7 +1061,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D8" s="3" t="n">
         <v>26.8</v>
       </c>
@@ -1065,7 +1071,7 @@
         <v>18.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>8.4</v>
@@ -1074,10 +1080,10 @@
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.4</v>
@@ -1105,13 +1111,13 @@
         <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>66.2</v>
+        <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>24.6</v>
+        <v>2.4</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1120,10 +1126,10 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>59.2</v>
+        <v>69.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1143,13 +1149,13 @@
         <v>147.4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>51.8</v>
+        <v>54.8</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>5.7</v>
@@ -1158,13 +1164,13 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.6</v>
+        <v>16.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>47.1</v>
+        <v>944.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>92.59999999999999</v>
@@ -1173,7 +1179,7 @@
         <v>100.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.6</v>
+        <v>452.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1185,16 +1191,16 @@
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>129.8</v>
+        <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>11</v>
@@ -1203,7 +1209,7 @@
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
@@ -1219,7 +1225,9 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="D10" s="3" t="n">
         <v>29.5</v>
       </c>
@@ -1229,19 +1237,21 @@
       <c r="F10" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>19.6</v>
+      <c r="G10" s="8" t="n">
+        <v>91.59999999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>860.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
       </c>
@@ -1249,7 +1259,7 @@
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>91.2</v>
@@ -1270,7 +1280,7 @@
         <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>24.8</v>
@@ -1285,7 +1295,7 @@
         <v>2.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1314,55 +1324,53 @@
         <v>10.5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>13.6</v>
+        <v>1.8</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.7</v>
       </c>
       <c r="M11" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>21.6</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>65.7</v>
+      <c r="R11" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>61.2</v>
+        <v>6.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>16.8</v>
+        <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>81.2</v>
@@ -1382,22 +1390,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.1</v>
+        <v>5.1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28.1</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>81.5</v>
+        <v>17.3</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>1.6</v>
@@ -1406,7 +1414,7 @@
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>19</v>
@@ -1414,7 +1422,7 @@
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1424,34 +1432,34 @@
         <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>25.8</v>
+        <v>2.5</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>67.2</v>
+        <v>61.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>164.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1474,19 +1482,19 @@
         <v>13.5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2.2</v>
+        <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>12.6</v>
+        <v>17.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>27.5</v>
+        <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
@@ -1498,7 +1506,7 @@
         <v>18.3</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>25.3</v>
+        <v>24.3</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1507,7 +1515,7 @@
         <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>20.4</v>
@@ -1519,7 +1527,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1549,9 +1557,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>133.1</v>
-      </c>
+      <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="n">
         <v>29.9</v>
       </c>
@@ -1559,12 +1565,12 @@
         <v>18.4</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>14.2</v>
+        <v>24.2</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1580,28 +1586,26 @@
         <v>18.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
+        <v>19.7</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>21.4</v>
+        <v>31.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>5.8</v>
+        <v>88.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1616,10 +1620,10 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>17.2</v>
+        <v>717.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>951.4</v>
+        <v>51.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1634,12 +1638,14 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="8" t="n">
-        <v>891.9</v>
+      <c r="C15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>29.5</v>
@@ -1651,28 +1657,28 @@
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>12.1</v>
+        <v>29.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>2.6</v>
@@ -1680,8 +1686,8 @@
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>4.8</v>
+      <c r="S15" s="8" t="n">
+        <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1692,8 +1698,8 @@
       <c r="V15" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>9.5</v>
+      <c r="W15" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.4</v>
@@ -1702,7 +1708,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1719,28 +1725,28 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="n">
-        <v>140.8</v>
+        <v>1940.4</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>92.3</v>
+        <v>44.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>116.6</v>
+        <v>114.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>17.3</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>951.3</v>
@@ -1752,35 +1758,35 @@
         <v>10.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>9455.200000000001</v>
+        <v>453.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>16.2</v>
+        <v>122.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1182.9</v>
+        <v>1127.3</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>21314.2</v>
+        <v>18.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1158.5</v>
+        <v>984.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>11274.6</v>
+        <v>1124.6</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>100.5</v>
+        <v>10064.6</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1796,17 +1802,15 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="n">
-        <v>28.9</v>
+        <v>29.9</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.6</v>
@@ -1818,41 +1822,39 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="M17" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="M17" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
         <v>9.1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>51.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>35.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>222.3</v>
+        <v>22.7</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>21.5</v>
@@ -1878,23 +1880,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="8" t="n">
-        <v>8.9</v>
+      <c r="D18" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>12.8</v>
+        <v>18.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>24.9</v>
+        <v>25.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>12.9</v>
+        <v>1.2</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>15.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>2.6</v>
@@ -1903,10 +1905,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
@@ -1916,7 +1918,7 @@
         <v>0.2</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>2.1</v>
+        <v>29.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.2</v>
@@ -1925,16 +1927,16 @@
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>54.8</v>
+        <v>94.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>10.4</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>24.3</v>
@@ -1956,9 +1958,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="8" t="n">
-        <v>9.699999999999999</v>
+      <c r="C19" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
@@ -1970,7 +1974,7 @@
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>16.5</v>
+        <v>46.9</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.3</v>
@@ -1981,8 +1985,8 @@
       <c r="K19" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>418.3</v>
+      <c r="L19" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>18.2</v>
@@ -2001,13 +2005,13 @@
         <v>19.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>2.4</v>
+        <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
@@ -2035,14 +2039,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>85.3</v>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>23.7</v>
@@ -2066,9 +2068,11 @@
         <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>19.2</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O20" s="3" t="n">
         <v>90.2</v>
       </c>
@@ -2082,22 +2086,22 @@
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>82.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>41.8</v>
+        <v>81.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2118,7 +2122,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="n">
-        <v>28.7</v>
+        <v>1.5</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2127,10 +2131,10 @@
         <v>21.2</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2139,7 +2143,7 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>7.8</v>
+        <v>73.8</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>19.4</v>
@@ -2155,19 +2159,19 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>19.2</v>
+        <v>11.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>13.5</v>
@@ -2195,25 +2199,25 @@
       </c>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>29.9</v>
+        <v>37.4</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>23.2</v>
+      <c r="F22" s="8" t="n">
+        <v>32.8</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.2</v>
+        <v>23.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2222,10 +2226,10 @@
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>10.8</v>
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99.2</v>
@@ -2243,7 +2247,7 @@
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>856.2</v>
+        <v>8956.200000000001</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
@@ -2274,57 +2278,55 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>1944.6</v>
+        <v>194.4</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>910.4</v>
+        <v>10.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>112.8</v>
+        <v>119.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>57.2</v>
+        <v>5.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>220.8</v>
+        <v>85.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>72.5</v>
+        <v>2.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>21.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>931.2</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
         <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>107.2</v>
+        <v>107.9</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>96</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>47.9</v>
@@ -2333,13 +2335,13 @@
         <v>108.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>197.4</v>
+        <v>19.7</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>118.8</v>
+        <v>94927.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
@@ -2356,58 +2358,58 @@
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="8" t="n">
-        <v>82.5</v>
+      <c r="D24" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="G24" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>58.9</v>
+        <v>8.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>98.8</v>
+        <v>88.8</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>531.2</v>
+        <v>581.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>21</v>
+      </c>
+      <c r="S24" s="8" t="n">
+        <v>823.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>12.2</v>
+        <v>78.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="8" t="n">
-        <v>81.7</v>
+      <c r="V24" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>20.5</v>
@@ -2430,40 +2432,40 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D25" s="3" t="n">
-        <v>29.8</v>
+        <v>21.2</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>11.1</v>
-      </c>
+        <v>24.2</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+        <v>42.4</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>15.5</v>
+        <v>24.2</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2478,22 +2480,22 @@
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>29.9</v>
+        <v>23.1</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>67.8</v>
+        <v>71.3</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>59.1</v>
+        <v>9.1</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2510,8 +2512,8 @@
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="n">
-        <v>28.6</v>
+      <c r="D26" s="8" t="n">
+        <v>98.59999999999999</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>19.2</v>
@@ -2523,7 +2525,7 @@
         <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.7</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.2</v>
@@ -2532,34 +2534,32 @@
         <v>1.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>92.59999999999999</v>
+        <v>2.3</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>71.8</v>
-      </c>
+        <v>20.6</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>23.9</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>47.9</v>
+        <v>27.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>26.2</v>
+        <v>76.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2590,14 +2590,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>22.4</v>
@@ -2606,37 +2604,37 @@
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>91.2</v>
+        <v>18.8</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>2.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
@@ -2645,9 +2643,9 @@
         <v>63.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V27" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W27" s="3" t="inlineStr"/>
@@ -2655,7 +2653,7 @@
         <v>80.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -2673,43 +2671,43 @@
       </c>
       <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>32.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>14.9</v>
+        <v>1.5</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.6</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>21.1</v>
+        <v>0.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>122.2</v>
+        <v>1272.4</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>20.1</v>
@@ -2717,26 +2715,26 @@
       <c r="R28" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="S28" s="8" t="n">
-        <v>74</v>
+      <c r="S28" s="3" t="n">
+        <v>27.6</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>61.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W28" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>17.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -2763,13 +2761,13 @@
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>11</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>9.800000000000001</v>
@@ -2781,13 +2779,11 @@
         <v>19.2</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>4.8</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="n">
-        <v>40.3</v>
+        <v>40.7</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>8</v>
@@ -2798,7 +2794,7 @@
       <c r="R29" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
@@ -2811,13 +2807,13 @@
         <v>20.1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>28.8</v>
+        <v>21.8</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>86.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="inlineStr"/>
       <c r="AA29" s="3" t="inlineStr">
@@ -2833,17 +2829,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>1948.4</v>
+        <v>149.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>118.1</v>
+        <v>119.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2858,47 +2852,47 @@
         <v>11.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>12.4</v>
+        <v>92.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>18.6</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>920.7</v>
+        <v>130.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>112.9</v>
+        <v>112.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>3322.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1088.1</v>
+        <v>118.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1184.1</v>
+        <v>18.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.6</v>
+        <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>108.4</v>
+        <v>374.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -2915,14 +2909,14 @@
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="8" t="n">
-        <v>39.7</v>
+      <c r="D31" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>11.9</v>
@@ -2937,35 +2931,35 @@
         <v>1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
-        <v>1</v>
+      <c r="L31" s="8" t="n">
+        <v>10.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>22.5</v>
+      <c r="R31" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.6</v>
@@ -2977,7 +2971,7 @@
         <v>77.3</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>14.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z31" s="3" t="inlineStr"/>
       <c r="AA31" s="3" t="inlineStr">
@@ -2995,40 +2989,38 @@
       </c>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>12.8</v>
+        <v>34.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2.5</v>
+        <v>25.6</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="H32" s="8" t="n">
-        <v>11.8</v>
+      <c r="H32" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>29.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -3037,15 +3029,15 @@
         <v>29.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="U32" s="8" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
@@ -3055,7 +3047,7 @@
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="inlineStr"/>
@@ -3072,14 +3064,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="C33" s="3" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>32.6</v>
+        <v>4.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>2.5</v>
@@ -3091,7 +3081,7 @@
         <v>17.9</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.5</v>
@@ -3099,17 +3089,15 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N33" s="3" t="n">
+      <c r="M33" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="n">
         <v>10.8</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>59.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3118,28 +3106,28 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.6</v>
+        <v>12.8</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>15</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>21.4</v>
+        <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>165.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="inlineStr"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3155,14 +3143,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="C34" s="3" t="inlineStr"/>
       <c r="D34" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>25.8</v>
@@ -3177,28 +3163,28 @@
         <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>51.1</v>
+      <c r="M34" s="8" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3207,10 +3193,10 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>68.2</v>
+        <v>69.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3222,7 +3208,7 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="inlineStr"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3240,19 +3226,19 @@
       </c>
       <c r="C35" s="3" t="inlineStr"/>
       <c r="D35" s="3" t="n">
-        <v>0.4</v>
+        <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.8</v>
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>10.2</v>
+        <v>18.2</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>1.9</v>
@@ -3264,16 +3250,16 @@
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>30.1</v>
+        <v>1.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>994.2</v>
+        <v>172.4</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3288,13 +3274,13 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>12.2</v>
+        <v>192.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
@@ -3303,7 +3289,7 @@
         <v>62.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>113.2</v>
+        <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
@@ -3321,25 +3307,25 @@
       </c>
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="n">
-        <v>33.6</v>
+        <v>1.3</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>15.6</v>
+        <v>1.5</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3347,12 +3333,12 @@
       <c r="L36" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M36" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>470.6</v>
+        <v>70.7</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
@@ -3361,13 +3347,13 @@
         <v>31.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>2.8</v>
@@ -3379,10 +3365,10 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>55.7</v>
+        <v>8.5</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3400,70 +3386,70 @@
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="3" t="n">
-        <v>1161.5</v>
+        <v>161.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>126.9</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>9.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>818</v>
+        <v>81</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>20.3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>49.9</v>
+        <v>949.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>28.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>721</v>
+        <v>92</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>950.6</v>
+        <v>950.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>120.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.6</v>
+        <v>1230.4</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>101</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>124.1</v>
+        <v>12.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>129.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>3672.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>537.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3486,33 +3472,33 @@
       <c r="E38" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>524.6</v>
+      <c r="F38" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="H38" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>14.5</v>
+        <v>9.9</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>7.2</v>
+        <v>46.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>50.7</v>
+        <v>30.2</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.2</v>
@@ -3524,7 +3510,7 @@
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.9</v>
+        <v>28.1</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>14.9</v>
@@ -3533,7 +3519,7 @@
         <v>24.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>82.2</v>
+        <v>22.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3542,7 +3528,7 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3563,35 +3549,35 @@
         <v>32.2</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>10.2</v>
+        <v>18.5</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>19</v>
+        <v>17.9</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>81</v>
+        <v>19.9</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>13</v>
+        <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>796</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3599,26 +3585,26 @@
       <c r="Q39" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="3" t="n">
         <v>42.6</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>61.6</v>
+        <v>69.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Y39" s="3" t="inlineStr"/>
       <c r="Z39" s="3" t="inlineStr"/>
@@ -3643,22 +3629,22 @@
         <v>18.3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
@@ -3666,8 +3652,8 @@
       <c r="M40" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>11.8</v>
+      <c r="N40" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3675,17 +3661,17 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S40" s="8" t="n">
-        <v>60.8</v>
+      <c r="Q40" s="8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>192.6</v>
+        <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>22.8</v>
@@ -3693,11 +3679,11 @@
       <c r="V40" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>51.8</v>
+      <c r="W40" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>26.9</v>
+        <v>8.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
@@ -3717,11 +3703,11 @@
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>25.4</v>
@@ -3736,24 +3722,22 @@
         <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>4.9</v>
+      <c r="L41" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>99.2</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="n">
         <v>2.4</v>
       </c>
@@ -3764,19 +3748,19 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>11.8</v>
+        <v>2.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.2</v>
+        <v>2.4</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>2.2</v>
+        <v>68.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3799,36 +3783,34 @@
       <c r="D42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>18.8</v>
+      <c r="E42" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2.5</v>
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>10.6</v>
+        <v>12.5</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>950.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="L42" s="8" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -3841,12 +3823,14 @@
       <c r="R42" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="S42" s="8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr"/>
-      <c r="U42" s="8" t="n">
-        <v>1</v>
+      <c r="S42" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="V42" s="3" t="inlineStr"/>
       <c r="W42" s="3" t="inlineStr"/>
@@ -3952,34 +3936,34 @@
         <v>24.6</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>18.8</v>
+        <v>5.4</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.9</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>14.1</v>
+        <v>141.1</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>89</v>
+        <v>8.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>266.6</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
@@ -3992,22 +3976,22 @@
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>509.7</v>
+        <v>32.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>96.2</v>
+        <v>95.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>818.7</v>
+        <v>22.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>966.3</v>
+        <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>271.2</v>
+        <v>221.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4034,7 +4018,7 @@
         <v>25.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>93.7</v>
+        <v>13.7</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>17.5</v>
@@ -4042,21 +4026,23 @@
       <c r="I46" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
-        <v>18.1</v>
+      <c r="J46" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>42.7</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>19.3</v>
+        <v>11.9</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4079,10 +4065,10 @@
         <v>24.2</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1211101.1</v>
+        <v>87208.5</v>
       </c>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>31.7</v>
+        <v>39.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>16.9</v>
@@ -767,10 +767,10 @@
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>8.4</v>
+        <v>28.8</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.8</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -782,16 +782,16 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>25.2</v>
+        <v>2.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>45.2</v>
+        <v>4.5</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>27.5</v>
+        <v>21.5</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
@@ -812,35 +812,33 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="n">
-        <v>25.2</v>
+        <v>26.2</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>26.8</v>
+        <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>17.6</v>
+        <v>11.6</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>17.6</v>
@@ -864,13 +862,13 @@
         <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>10.2</v>
+        <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v>43.9</v>
+        <v>6.5</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>21.3</v>
@@ -879,7 +877,7 @@
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>16.2</v>
+        <v>7.6</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -902,9 +900,9 @@
         <v>32.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -917,7 +915,7 @@
         <v>2.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>1.6</v>
@@ -929,13 +927,13 @@
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>15.8</v>
+        <v>1.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>91.2</v>
+        <v>921.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
@@ -947,22 +945,22 @@
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>20.6</v>
+        <v>390.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>14.4</v>
+        <v>17.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>21.3</v>
+        <v>22.6</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>17.8</v>
+        <v>27.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -981,20 +979,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="8" t="n">
         <v>30.5</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.5</v>
+        <v>25.2</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>79.8</v>
+      <c r="H7" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1003,22 +1001,24 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>20.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="R7" s="3" t="n">
@@ -1028,7 +1028,7 @@
         <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>87.2</v>
+        <v>81.2</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0.9</v>
@@ -1040,13 +1040,13 @@
         <v>20.6</v>
       </c>
       <c r="X7" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Z7" s="3" t="n">
         <v>23.8</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>11.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1061,9 +1061,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="n">
         <v>26.8</v>
       </c>
@@ -1071,7 +1069,7 @@
         <v>18.4</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>22.6</v>
+        <v>42.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>8.4</v>
@@ -1080,7 +1078,7 @@
         <v>17.3</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>2.2</v>
@@ -1096,10 +1094,10 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>91.2</v>
+        <v>791.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>25.8</v>
@@ -1111,13 +1109,13 @@
         <v>24.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>6.6</v>
+        <v>66.2</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>2.4</v>
+        <v>24.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>21.4</v>
@@ -1126,10 +1124,10 @@
         <v>23.6</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>69.2</v>
+        <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.3</v>
+        <v>27.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1146,40 +1144,40 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>147.4</v>
+        <v>147.9</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>118.5</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>54.8</v>
+        <v>57.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>944.1</v>
+        <v>44.1</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>3972.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>100.1</v>
+        <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>452.5</v>
+        <v>451.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1188,10 +1186,10 @@
         <v>129.4</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>110.9</v>
+        <v>110.1</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>122</v>
+        <v>122.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>318.6</v>
@@ -1209,9 +1207,11 @@
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1225,32 +1225,30 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <v>91.59999999999999</v>
+      <c r="G10" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>18.5</v>
@@ -1259,13 +1257,13 @@
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>91.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>25.9</v>
@@ -1277,7 +1275,7 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1292,10 +1290,10 @@
         <v>2.5</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>6.2</v>
+        <v>62.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1311,63 +1309,59 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="8" t="n">
         <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G11" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>19.7</v>
-      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
-        <v>0.7</v>
+        <v>8.4</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>18.3</v>
+        <v>24.3</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>91.59999999999999</v>
+      </c>
       <c r="P11" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>2.3</v>
+        <v>29.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>22.7</v>
+        <v>28.9</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>26.8</v>
@@ -1375,7 +1369,9 @@
       <c r="Y11" s="3" t="n">
         <v>81.2</v>
       </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="n">
+        <v>4.5</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1389,9 +1385,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="n">
         <v>26.4</v>
       </c>
@@ -1402,37 +1396,37 @@
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>984.1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>19</v>
+        <v>1.9</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22.6</v>
+        <v>2.5</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.2</v>
+        <v>2.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1441,25 +1435,25 @@
         <v>2.5</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>24.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>83.2</v>
+        <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6.5</v>
+        <v>82.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1479,13 +1473,13 @@
         <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.9</v>
+        <v>89.3</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1494,22 +1488,22 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>24.3</v>
+        <v>0.4</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
@@ -1527,7 +1521,7 @@
         <v>14.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3.8</v>
+        <v>31.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1539,10 +1533,10 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>85.2</v>
+        <v>12</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.3</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1557,7 +1551,9 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D14" s="3" t="n">
         <v>29.9</v>
       </c>
@@ -1571,24 +1567,26 @@
         <v>19.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
       </c>
@@ -1602,16 +1600,16 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>2.6</v>
+        <v>25.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>88.2</v>
+        <v>58.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V14" s="8" t="n">
-        <v>15.1</v>
+      <c r="V14" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>22.8</v>
@@ -1620,7 +1618,7 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>717.2</v>
+        <v>27.2</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>51.4</v>
@@ -1638,32 +1636,30 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>29.5</v>
+      <c r="F15" s="8" t="n">
+        <v>93.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.5</v>
+        <v>9.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19</v>
@@ -1672,13 +1668,13 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>29.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.5</v>
+        <v>91.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>2.6</v>
@@ -1686,8 +1682,8 @@
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S15" s="8" t="n">
-        <v>22.7</v>
+      <c r="S15" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1696,7 +1692,7 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>21.4</v>
+        <v>28.4</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>20.9</v>
@@ -1708,7 +1704,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1725,70 +1721,72 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="n">
-        <v>1940.4</v>
+        <v>14</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>44.3</v>
+        <v>112.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>114.6</v>
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>48.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.5</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>3.2</v>
-      </c>
+        <v>14.3</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
-        <v>951.3</v>
+        <v>95.3</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>10.1</v>
+        <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>453.2</v>
+        <v>853.2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>122.2</v>
+        <v>127.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1127.3</v>
+        <v>122.3</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>18.2</v>
+        <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>984.8</v>
+        <v>187.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1124.6</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>10.8</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>124.6</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>10064.6</v>
-      </c>
-      <c r="Z16" s="3" t="inlineStr"/>
+        <v>970.8</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1804,16 +1802,16 @@
       </c>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="n">
-        <v>29.9</v>
+        <v>28.4</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>19.3</v>
+        <v>18.3</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>23.3</v>
+        <v>1.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1822,39 +1820,41 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4.8</v>
+        <v>22.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>9.1</v>
+        <v>21.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="8" t="n">
-        <v>51.8</v>
+      <c r="Q17" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>35.3</v>
+      <c r="S17" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>64.2</v>
+        <v>6.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>21.5</v>
@@ -1863,9 +1863,11 @@
         <v>24.8</v>
       </c>
       <c r="Y17" s="3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1884,22 +1886,22 @@
         <v>30.9</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1910,15 +1912,17 @@
       <c r="M18" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>91.2</v>
+        <v>291.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>29.2</v>
+        <v>89.2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>23.2</v>
@@ -1927,10 +1931,10 @@
         <v>26</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>94.2</v>
+        <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
+        <v>1</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21.8</v>
@@ -1939,12 +1943,14 @@
         <v>20.8</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>24.3</v>
+        <v>25.3</v>
       </c>
       <c r="Y18" s="3" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="Z18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" s="3" t="inlineStr"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -1959,25 +1965,25 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>24.1</v>
+        <v>2.4</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46.9</v>
+        <v>15.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>2.5</v>
@@ -1989,9 +1995,11 @@
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
+        <v>18.6</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -2011,21 +2019,23 @@
         <v>20.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10.8</v>
+        <v>1</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>19.9</v>
+        <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z19" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Z19" s="3" t="inlineStr"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2039,18 +2049,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="D20" s="3" t="n">
-        <v>22.3</v>
+        <v>28.3</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>9.6</v>
+      <c r="G20" s="8" t="n">
+        <v>59.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2062,19 +2074,17 @@
         <v>2.8</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>19.2</v>
+        <v>0</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>18.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
-        <v>90.2</v>
+        <v>99.2</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0</v>
@@ -2086,27 +2096,29 @@
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>22.7</v>
+        <v>20.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>72.2</v>
+        <v>22.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>81.8</v>
+        <v>22.8</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="3" t="n">
-        <v>22.1</v>
+      <c r="X20" s="8" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2120,21 +2132,23 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D21" s="3" t="n">
-        <v>1.5</v>
+        <v>28.9</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>21.2</v>
+        <v>23.2</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.7</v>
+        <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>1</v>
@@ -2143,7 +2157,7 @@
         <v>1.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>73.8</v>
+        <v>3.8</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>19.4</v>
@@ -2159,31 +2173,35 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>11.2</v>
+        <v>19.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.3</v>
+        <v>88.7</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="W21" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="X21" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2197,15 +2215,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D22" s="3" t="n">
-        <v>37.4</v>
+        <v>29.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>32.8</v>
+        <v>17.8</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
@@ -2217,54 +2237,56 @@
         <v>11.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>18</v>
+        <v>1.8</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>11.8</v>
+        <v>0.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.2</v>
+        <v>991.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>28.5</v>
+        <v>2.9</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>8956.200000000001</v>
+        <v>86.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>24.6</v>
+        <v>2.4</v>
       </c>
       <c r="W22" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X22" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X22" s="3" t="n">
+      <c r="Y22" s="3" t="n">
         <v>80.2</v>
       </c>
-      <c r="Y22" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2280,70 +2302,72 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>194.4</v>
+        <v>1942.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>119.2</v>
+        <v>112.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.2</v>
+        <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.8</v>
+        <v>23.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>93.90000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>1952.9</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>43.1</v>
+        <v>951.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
         <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>107.9</v>
+        <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>360.2</v>
+        <v>36</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>47.9</v>
+        <v>37.7</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>108.6</v>
+        <v>108.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>19.7</v>
+        <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>94927.8</v>
+        <v>198.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="Z23" s="3" t="inlineStr"/>
+        <v>9425.6</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2357,7 +2381,9 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D24" s="3" t="n">
         <v>28.5</v>
       </c>
@@ -2374,51 +2400,59 @@
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>65.59999999999999</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="M24" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>581.2</v>
+        <v>91.2</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>823.9</v>
+        <v>21.6</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>78.2</v>
+        <v>72.3</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="8" t="n">
         <v>21.7</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="X24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="n">
+        <v>23.5</v>
+      </c>
       <c r="Y24" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="n">
+        <v>85.8</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2432,70 +2466,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>444.1</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N25" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="O25" s="3" t="n">
-        <v>24.2</v>
+        <v>59.2</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>25.8</v>
+        <v>2.6</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="X25" s="8" t="n">
-        <v>71.3</v>
+        <v>4.9</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>9.1</v>
+        <v>69.3</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2511,18 +2547,20 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="8" t="n">
-        <v>98.59999999999999</v>
+      <c r="C26" s="3" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>1.6</v>
@@ -2534,17 +2572,19 @@
         <v>1.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>19.6</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>989.6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2553,10 +2593,10 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.9</v>
+        <v>17.9</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2565,10 +2605,10 @@
         <v>5.9</v>
       </c>
       <c r="V26" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>21.3</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>24.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>86.2</v>
@@ -2576,7 +2616,9 @@
       <c r="Y26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Z26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="n">
+        <v>24.5</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2601,40 +2643,40 @@
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.9</v>
+        <v>19.8</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.4</v>
+        <v>922.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2.6</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>23.9</v>
@@ -2643,19 +2685,23 @@
         <v>63.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="V27" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="W27" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W27" s="3" t="inlineStr"/>
       <c r="X27" s="3" t="n">
-        <v>80.2</v>
+        <v>24</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="n">
+        <v>80.2</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2670,17 +2716,17 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="8" t="n">
         <v>32.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.5</v>
+        <v>17.9</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2692,51 +2738,53 @@
         <v>5.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>16.8</v>
+        <v>1.6</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.1</v>
+        <v>14.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1272.4</v>
+        <v>92.2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.1</v>
+        <v>20.9</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2.3</v>
+        <v>23.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.6</v>
+        <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>40.2</v>
+        <v>4</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W28" s="8" t="n">
-        <v>22.8</v>
+        <v>21</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>53.4</v>
+        <v>21.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>14.6</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>53.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2758,19 +2806,19 @@
         <v>18.4</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11.7</v>
+        <v>19.7</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.5</v>
@@ -2778,15 +2826,15 @@
       <c r="L29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M29" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>40.7</v>
+        <v>90.2</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>22.4</v>
@@ -2795,7 +2843,7 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>12.2</v>
@@ -2804,7 +2852,7 @@
         <v>2.5</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>20.1</v>
+        <v>13.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2815,7 +2863,9 @@
       <c r="Y29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2831,16 +2881,16 @@
       </c>
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>149.4</v>
+        <v>1498.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8.9</v>
+        <v>189.6</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>119.1</v>
+        <v>11.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>58.8</v>
+        <v>5.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
@@ -2849,20 +2899,20 @@
         <v>10.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.8</v>
+        <v>17.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>92.5</v>
+        <v>292.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>392.1</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2871,7 +2921,7 @@
         <v>130.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>112.7</v>
+        <v>112.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
@@ -2883,18 +2933,20 @@
         <v>118.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>18.4</v>
+        <v>104.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>117.6</v>
+        <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>374.2</v>
+        <v>312.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>52.4</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>33</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2913,32 +2965,32 @@
         <v>29.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>11.9</v>
+        <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>25.5</v>
+        <v>28.4</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -2947,33 +2999,35 @@
         <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>82.8</v>
+        <v>26.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>25.6</v>
+        <v>20.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>77.3</v>
+        <v>22.7</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>47.8</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>23.6</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2987,43 +3041,45 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="n">
-        <v>34.8</v>
+      <c r="C32" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>232.8</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>25.6</v>
+        <v>85</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>29.1</v>
+        <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>9.6</v>
+        <v>0.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>29.9</v>
@@ -3035,21 +3091,23 @@
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>35.2</v>
+        <v>3.5</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
+        <v>85.3</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>22.4</v>
+      </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3064,9 +3122,11 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="D33" s="3" t="n">
-        <v>4.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
@@ -3089,15 +3149,15 @@
       <c r="K33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3106,19 +3166,19 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>12.8</v>
+        <v>7.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15</v>
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>27.4</v>
@@ -3129,7 +3189,9 @@
       <c r="Y33" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3148,15 +3210,15 @@
         <v>32.1</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>13.4</v>
+        <v>19.4</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>25.8</v>
+        <v>26.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" s="8" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3166,25 +3228,25 @@
         <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>91.90000000000001</v>
+      <c r="M34" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3193,10 +3255,10 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>69.2</v>
+        <v>61.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2</v>
+        <v>23.9</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3208,9 +3270,11 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3224,7 +3288,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D35" s="3" t="n">
         <v>30.4</v>
       </c>
@@ -3250,21 +3316,21 @@
         <v>1.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>11.1</v>
+        <v>1.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>172.4</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3274,7 +3340,7 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>192.2</v>
+        <v>129.2</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>2.5</v>
@@ -3291,7 +3357,9 @@
       <c r="Y35" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="n">
+        <v>33.6</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3306,11 +3374,11 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="n">
-        <v>1.3</v>
+      <c r="D36" s="8" t="n">
+        <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>25.8</v>
@@ -3325,38 +3393,40 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>18.7</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>70.7</v>
+        <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="3" t="n">
-        <v>23</v>
+      <c r="R36" s="8" t="n">
+        <v>35</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>12.5</v>
+        <v>48.2</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>2.8</v>
+        <v>28.3</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>23.9</v>
@@ -3365,12 +3435,14 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>8.5</v>
+        <v>85.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3389,7 +3461,7 @@
         <v>161.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>1929.5</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>126.9</v>
@@ -3398,60 +3470,62 @@
         <v>69.40000000000001</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>81</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2</v>
+        <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>949.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>951.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>92</v>
+        <v>0.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.5</v>
+        <v>11.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>950.2</v>
+        <v>150.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>2.6</v>
+        <v>28.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>119</v>
+        <v>117.3</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1230.4</v>
+        <v>120.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>12.4</v>
+        <v>124.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>129.9</v>
+        <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7367.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
-      <c r="Z37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="n">
+        <v>247.3</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3473,7 +3547,7 @@
         <v>18.4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>25.4</v>
+        <v>2.5</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3485,20 +3559,20 @@
         <v>2.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.9</v>
+        <v>4.1</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>46.8</v>
+        <v>17.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0.2</v>
+        <v>18.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>30.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>1.2</v>
@@ -3506,20 +3580,20 @@
       <c r="Q38" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>28.1</v>
+        <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22.2</v>
+        <v>82.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
@@ -3528,9 +3602,11 @@
         <v>13.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3546,38 +3622,38 @@
       </c>
       <c r="C39" s="3" t="inlineStr"/>
       <c r="D39" s="3" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>18.5</v>
+        <v>45.3</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>8.5</v>
+        <v>25.6</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M39" s="8" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>796</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3586,28 +3662,32 @@
         <v>26.4</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>42.6</v>
+        <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>25.1</v>
+        <v>22.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>69.2</v>
+        <v>61.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>27.8</v>
+        <v>21.9</v>
       </c>
       <c r="V39" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z39" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W39" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr"/>
-      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3621,7 +3701,9 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D40" s="3" t="n">
         <v>32.5</v>
       </c>
@@ -3629,31 +3711,31 @@
         <v>18.3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>25.4</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>13.8</v>
+        <v>1.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>11.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3661,34 +3743,36 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="8" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R40" s="8" t="n">
-        <v>82.2</v>
+      <c r="Q40" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19.2</v>
+        <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>22.8</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>28.6</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>8.6</v>
+        <v>21.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="n">
+        <v>826.2</v>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3704,10 +3788,10 @@
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="3" t="n">
-        <v>21.8</v>
+        <v>31.8</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>25.4</v>
@@ -3716,30 +3800,32 @@
         <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
+        <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>20.9</v>
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+        <v>81.2</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="Q41" s="3" t="n">
-        <v>2.4</v>
+        <v>29.4</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3748,24 +3834,26 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>2.4</v>
+        <v>37.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>22.8</v>
+        <v>9</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>2.4</v>
+        <v>21.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>68.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3780,37 +3868,37 @@
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>32.4</v>
       </c>
-      <c r="E42" s="8" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="F42" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="H42" s="3" t="n">
-        <v>11.8</v>
+        <v>1.3</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>8.6</v>
+      <c r="J42" s="8" t="n">
+        <v>72.8</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="L42" s="8" t="n">
-        <v>98.40000000000001</v>
+      <c r="L42" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>13.3</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -3818,22 +3906,26 @@
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>82</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>27.6</v>
+        <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>21.4</v>
+        <v>11.6</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V42" s="3" t="inlineStr"/>
-      <c r="W42" s="3" t="inlineStr"/>
+        <v>8.6</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -3936,64 +4028,66 @@
         <v>24.6</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>5.4</v>
+        <v>54.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>62.8</v>
+        <v>69.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>141.1</v>
+        <v>111.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>8.9</v>
-      </c>
+        <v>111.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>26.6</v>
+        <v>2366.2</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="n">
+        <v>106.9</v>
+      </c>
       <c r="R45" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>32.7</v>
+        <v>132.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>95.2</v>
+        <v>1.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>22.9</v>
+        <v>892.7</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>221.2</v>
+        <v>19327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>21.4</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4009,68 +4103,72 @@
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="n">
-        <v>22.3</v>
+        <v>1.1</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>18.7</v>
+        <v>32.3</v>
       </c>
       <c r="F46" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>25.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>13.7</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>4.1</v>
+        <v>30.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>42.7</v>
+        <v>0.4</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>92.3</v>
       </c>
       <c r="P46" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
       <c r="R46" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>87208.5</v>
-      </c>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="n">
+        <v>992.9</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="n">
-        <v>39.7</v>
+        <v>31.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>16.9</v>
@@ -767,10 +767,10 @@
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>2.5</v>
+        <v>25.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>4.5</v>
@@ -791,7 +791,7 @@
         <v>18.6</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>21.5</v>
+        <v>27.5</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
@@ -820,10 +820,10 @@
         <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>21.8</v>
+        <v>26.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>81.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>17.3</v>
@@ -838,7 +838,7 @@
         <v>8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>11.6</v>
+        <v>17.6</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>17.6</v>
@@ -847,7 +847,7 @@
         <v>2</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>91.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>23.1</v>
@@ -877,7 +877,7 @@
         <v>29.9</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6.8</v>
@@ -900,9 +900,9 @@
         <v>32.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="F6" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -918,7 +918,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>17.4</v>
@@ -927,28 +927,28 @@
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.8</v>
+        <v>14.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>921.2</v>
+        <v>91.2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>24.9</v>
+        <v>24.1</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>390.6</v>
+        <v>50.6</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>17.4</v>
+        <v>14.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>27.2</v>
@@ -960,7 +960,7 @@
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>27.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="3" t="n">
         <v>30.5</v>
       </c>
       <c r="E7" s="3" t="n">
@@ -992,7 +992,7 @@
         <v>10.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>1.4</v>
@@ -1001,7 +1001,7 @@
         <v>2.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.2</v>
+        <v>15.8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.3</v>
@@ -1028,7 +1028,7 @@
         <v>2.2</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>81.2</v>
+        <v>87.2</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>0.9</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>791.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>86.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>27.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>147.9</v>
+        <v>147.4</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1162,7 +1162,7 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>44.1</v>
@@ -1171,13 +1171,13 @@
         <v>92.59999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>3972.6</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>451.2</v>
+        <v>454.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0.2</v>
@@ -1201,7 +1201,7 @@
         <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
@@ -1233,7 +1233,7 @@
         <v>17.9</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.3</v>
+        <v>23.7</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>11.6</v>
@@ -1245,7 +1245,7 @@
         <v>1.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.1</v>
@@ -1257,10 +1257,10 @@
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
@@ -1275,7 +1275,7 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>6.4</v>
+        <v>64</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1287,13 +1287,13 @@
         <v>22.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>2.5</v>
+        <v>25.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1.6</v>
+        <v>76.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>62.8</v>
+        <v>6.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="3" t="n">
         <v>29</v>
       </c>
       <c r="E11" s="3" t="n">
@@ -1323,15 +1323,15 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>24.3</v>
+      <c r="M11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1340,13 +1340,13 @@
         <v>91.59999999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>29.8</v>
+        <v>23.8</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>26.7</v>
@@ -1360,7 +1360,7 @@
       <c r="V11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="W11" s="8" t="n">
+      <c r="W11" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1396,64 +1396,64 @@
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>984.1</v>
+        <v>8.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>1.9</v>
+        <v>19</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>2.5</v>
+        <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>61.3</v>
+        <v>67.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>2.4</v>
+        <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>82.2</v>
+        <v>83.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1473,13 +1473,13 @@
         <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>89.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>17.6</v>
@@ -1488,22 +1488,22 @@
         <v>2.5</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>9</v>
+        <v>90.2</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.4</v>
@@ -1518,10 +1518,10 @@
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>14.2</v>
+        <v>84.2</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>31.8</v>
+        <v>3.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.2</v>
@@ -1533,10 +1533,10 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.5</v>
+        <v>10.1</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>29.9</v>
@@ -1564,7 +1564,7 @@
         <v>24.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>15.5</v>
@@ -1576,7 +1576,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1585,7 +1585,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.2</v>
+        <v>2.1</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1594,7 +1594,7 @@
         <v>0.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>31.4</v>
+        <v>27.7</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>23.4</v>
@@ -1603,7 +1603,7 @@
         <v>25.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58.2</v>
+        <v>5.8</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1618,10 +1618,10 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>27.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>51.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1643,17 +1643,17 @@
       <c r="E15" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>93.5</v>
+      <c r="F15" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1668,7 +1668,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1677,13 +1677,13 @@
         <v>0.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2.6</v>
+        <v>26.6</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1692,7 +1692,7 @@
         <v>9.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.4</v>
+        <v>21.4</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>20.9</v>
@@ -1704,7 +1704,7 @@
         <v>8.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1721,22 +1721,22 @@
       </c>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="n">
-        <v>14</v>
+        <v>140.4</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>112.3</v>
+        <v>12.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>116.6</v>
+        <v>116.5</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>29.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>14.3</v>
@@ -1752,16 +1752,16 @@
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>853.2</v>
+        <v>53.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>127.2</v>
+        <v>122.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>122.3</v>
+        <v>112.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1770,19 +1770,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>99.2</v>
+        <v>49.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>187.8</v>
+        <v>114</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>970.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1800,18 +1800,20 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="D17" s="3" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.5</v>
@@ -1820,20 +1822,20 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>22.9</v>
+        <v>2.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
+      <c r="L17" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>21.2</v>
+        <v>91.2</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
@@ -1848,10 +1850,10 @@
         <v>25.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6.4</v>
+        <v>64.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>22.9</v>
@@ -1895,7 +1897,7 @@
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1910,13 +1912,13 @@
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>291.2</v>
+        <v>91.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
@@ -1968,19 +1970,19 @@
         <v>1.1</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2.4</v>
+        <v>24.1</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.5</v>
@@ -1995,10 +1997,10 @@
         <v>18.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
@@ -2016,22 +2018,22 @@
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>20.2</v>
+        <v>90.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>19.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.8</v>
+        <v>87.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2050,19 +2052,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G20" s="8" t="n">
-        <v>59.6</v>
+      <c r="G20" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2076,11 +2078,11 @@
       <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="8" t="n">
-        <v>19.8</v>
+      <c r="L20" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
@@ -2096,10 +2098,10 @@
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>20.7</v>
+        <v>23.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.2</v>
+        <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.3</v>
@@ -2110,8 +2112,8 @@
       <c r="W20" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X20" s="8" t="n">
-        <v>23.2</v>
+      <c r="X20" s="3" t="n">
+        <v>85.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2136,7 +2138,7 @@
         <v>1.1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28.9</v>
+        <v>28.3</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2165,7 +2167,9 @@
       <c r="M21" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
       </c>
@@ -2176,28 +2180,28 @@
         <v>19.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>1.3</v>
+        <v>12.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.7</v>
+        <v>88.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2222,19 +2226,19 @@
         <v>29.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2.3</v>
+        <v>23.2</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.2</v>
@@ -2243,37 +2247,37 @@
         <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>991.2</v>
+        <v>91.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.9</v>
+        <v>28.5</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>2.2</v>
+        <v>23.1</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>25</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>86.2</v>
+        <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>2.4</v>
+        <v>24.6</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>26.2</v>
@@ -2302,40 +2306,40 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>1942.6</v>
+        <v>142.5</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>112.2</v>
+        <v>12.2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>52.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.6</v>
+        <v>7.6</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>28.7</v>
+        <v>51.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1952.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>951.2</v>
+        <v>458.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
@@ -2360,10 +2364,10 @@
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>198.7</v>
+        <v>117.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9425.6</v>
+        <v>27.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2382,7 +2386,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>28.5</v>
@@ -2400,16 +2404,16 @@
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>65.59999999999999</v>
+        <v>991999.1</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>98.8</v>
+        <v>18.8</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>18.6</v>
@@ -2418,7 +2422,7 @@
         <v>0.8</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.2</v>
@@ -2427,18 +2431,18 @@
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21.6</v>
+        <v>2.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="V24" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="W24" s="3" t="n">
@@ -2451,7 +2455,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2470,7 +2474,7 @@
       <c r="D25" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="F25" s="3" t="n">
@@ -2480,7 +2484,7 @@
         <v>444.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>2.1</v>
@@ -2492,19 +2496,19 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>12.9</v>
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>59.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>2.6</v>
@@ -2516,10 +2520,10 @@
         <v>26.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>31.2</v>
+        <v>71.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>25.3</v>
@@ -2528,10 +2532,10 @@
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>69.3</v>
+        <v>67.2</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2548,22 +2552,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>111.6</v>
+        <v>1.1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>9.4</v>
+        <v>28.4</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.6</v>
+        <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.2</v>
@@ -2577,14 +2581,14 @@
       <c r="L26" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M26" s="8" t="n">
-        <v>989.6</v>
+      <c r="M26" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2596,7 +2600,7 @@
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.9</v>
+        <v>27.1</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>76.2</v>
@@ -2643,19 +2647,19 @@
         <v>22.4</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.2</v>
+        <v>22.5</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
@@ -2664,16 +2668,16 @@
         <v>1.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>19.1</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>922.2</v>
+        <v>98.2</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2682,7 +2686,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>63.2</v>
+        <v>2.5</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2716,7 +2720,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="3" t="n">
         <v>32.7</v>
       </c>
       <c r="E28" s="3" t="n">
@@ -2726,7 +2730,7 @@
         <v>24.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>14</v>
@@ -2741,22 +2745,22 @@
         <v>0.3</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>14.8</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.9</v>
+        <v>20.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2765,7 +2769,7 @@
         <v>24.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4</v>
+        <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.2</v>
@@ -2774,10 +2778,10 @@
         <v>21</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>2.1</v>
+        <v>21.1</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>21.2</v>
+        <v>20.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2824,14 +2828,14 @@
         <v>0.5</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>90.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0</v>
@@ -2843,16 +2847,16 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>14.5</v>
+        <v>24.5</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>12.2</v>
+        <v>72.2</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>13.4</v>
+        <v>19.4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>21.8</v>
@@ -2864,7 +2868,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2881,22 +2885,22 @@
       </c>
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>1498.4</v>
+        <v>148.4</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>189.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>11.8</v>
+        <v>118.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.8</v>
+        <v>58.8</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>17.8</v>
@@ -2905,14 +2909,14 @@
         <v>8.300000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>292.5</v>
+        <v>92.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>392.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2921,28 +2925,28 @@
         <v>130.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>112.9</v>
+        <v>12.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>322.2</v>
+        <v>222.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>118.2</v>
+        <v>18.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>104.1</v>
+        <v>10.4</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>114.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>312.2</v>
+        <v>372.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>52.4</v>
+        <v>32.4</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>33</v>
@@ -2965,7 +2969,7 @@
         <v>29.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>23.9</v>
@@ -2974,23 +2978,23 @@
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.1</v>
+        <v>16.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>10.3</v>
+        <v>18.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>28.4</v>
+        <v>2.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -2999,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>22.6</v>
@@ -3017,10 +3021,10 @@
         <v>20.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>47.8</v>
+        <v>22.9</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>77.8</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>6.5</v>
@@ -3044,8 +3048,8 @@
       <c r="C32" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="D32" s="8" t="n">
-        <v>232.8</v>
+      <c r="D32" s="3" t="n">
+        <v>38.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>4.5</v>
@@ -3054,32 +3058,32 @@
         <v>85</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="3" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>29.9</v>
@@ -3091,13 +3095,13 @@
         <v>26.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>3.5</v>
+        <v>35.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>25.8</v>
@@ -3106,7 +3110,7 @@
         <v>85.3</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
@@ -3123,19 +3127,19 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>32.6</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>18</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>2.5</v>
+        <v>25.8</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.4</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3150,14 +3154,14 @@
         <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3166,28 +3170,28 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>78.2</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>15</v>
@@ -3205,7 +3209,9 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="D34" s="3" t="n">
         <v>32.1</v>
       </c>
@@ -3213,12 +3219,12 @@
         <v>19.4</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3237,16 +3243,16 @@
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>8.1</v>
+        <v>87.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20.9</v>
@@ -3255,10 +3261,10 @@
         <v>22.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>61.2</v>
+        <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3270,7 +3276,7 @@
         <v>86.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>9</v>
@@ -3289,13 +3295,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>27.4</v>
@@ -3319,18 +3325,18 @@
         <v>19</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>28</v>
       </c>
       <c r="R35" s="3" t="n">
@@ -3340,13 +3346,13 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>129.2</v>
+        <v>15.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>2.5</v>
+        <v>25.7</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.2</v>
@@ -3358,7 +3364,7 @@
         <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>33.6</v>
+        <v>33.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3374,8 +3380,8 @@
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="8" t="n">
-        <v>33.6</v>
+      <c r="D36" s="3" t="n">
+        <v>93.59999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19</v>
@@ -3405,25 +3411,25 @@
         <v>1.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R36" s="8" t="n">
-        <v>35</v>
+      <c r="R36" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>48.2</v>
+        <v>4.4</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
@@ -3435,7 +3441,7 @@
         <v>27</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>85.2</v>
+        <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>11.5</v>
@@ -3461,7 +3467,7 @@
         <v>161.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1929.5</v>
+        <v>92.5</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>126.9</v>
@@ -3479,34 +3485,34 @@
         <v>20.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>949.9</v>
+        <v>49.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>951.1</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.2</v>
+        <v>50.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>28.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>117.3</v>
+        <v>17.5</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>120.4</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>101.3</v>
+        <v>70.3</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>124.7</v>
@@ -3518,13 +3524,13 @@
         <v>125.9</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7367.2</v>
+        <v>267.2</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.3</v>
+        <v>24.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3541,13 +3547,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="n">
-        <v>12.3</v>
+        <v>92.3</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2.5</v>
+        <v>25.5</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3561,26 +3567,28 @@
       <c r="J38" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="n">
+        <v>555.5</v>
+      </c>
       <c r="L38" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3593,19 +3601,19 @@
         <v>24.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>82.2</v>
+        <v>22.2</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>13.2</v>
+        <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3633,7 +3641,7 @@
       <c r="G39" s="3" t="n">
         <v>45.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3643,17 +3651,17 @@
         <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>49</v>
+        <v>6.2</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3665,7 +3673,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.1</v>
+        <v>23.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3677,13 +3685,13 @@
         <v>20.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>2.4</v>
+        <v>241.7</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>22</v>
@@ -3711,19 +3719,19 @@
         <v>18.3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3732,10 +3740,10 @@
         <v>18.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>1.8</v>
+        <v>18.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3744,7 +3752,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3756,22 +3764,22 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>826.2</v>
+        <v>2.5</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3806,26 +3814,26 @@
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>9.1</v>
+      <c r="L41" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>81.2</v>
+        <v>91.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>29.4</v>
+        <v>24.1</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>22.8</v>
@@ -3834,7 +3842,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>37.8</v>
+        <v>59.2</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3852,7 +3860,7 @@
         <v>2.6</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3879,25 +3887,25 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1.3</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>72.8</v>
+      <c r="J42" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3906,25 +3914,25 @@
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>2.5</v>
+        <v>25</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>11.6</v>
+        <v>14.5</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>8.6</v>
+        <v>2.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>0.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4025,7 +4033,7 @@
         <v>122.3</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>24.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>102</v>
@@ -4040,50 +4048,50 @@
         <v>9.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>111.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>111.9</v>
+        <v>11.2</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>2366.2</v>
+        <v>26.6</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>106.9</v>
+        <v>106.7</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.2</v>
+        <v>241.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>132.7</v>
+        <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1.8</v>
+        <v>95.3</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>892.7</v>
+        <v>85.7</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>19327.2</v>
+        <v>232.7</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>8.199999999999999</v>
@@ -4109,7 +4117,7 @@
         <v>32.3</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>25.5</v>
@@ -4118,28 +4126,28 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J46" s="8" t="n">
-        <v>30.7</v>
+        <v>2.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.8</v>
+        <v>2.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>2.6</v>
+        <v>26.7</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>0.2</v>
@@ -4151,23 +4159,23 @@
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>2.4</v>
+        <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
-        <v>992.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -767,10 +758,10 @@
         <v>18.4</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>28.1</v>
+        <v>21.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -779,13 +770,13 @@
         <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>23.8</v>
+        <v>29.8</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>4.5</v>
+        <v>45.2</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>18.6</v>
@@ -820,7 +811,7 @@
         <v>17.4</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>26.8</v>
+        <v>21.8</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8.800000000000001</v>
@@ -844,7 +835,7 @@
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>2</v>
+        <v>20.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>91.59999999999999</v>
@@ -859,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>23.1</v>
+        <v>28.1</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>70.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>23.1</v>
@@ -903,7 +894,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>27.6</v>
+        <v>24.6</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15.2</v>
@@ -918,7 +909,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>17.4</v>
@@ -927,7 +918,7 @@
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>14.8</v>
+        <v>12.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>91.2</v>
@@ -960,7 +951,7 @@
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>77.2</v>
+        <v>37.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1025,7 +1016,7 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>87.2</v>
@@ -1094,7 +1085,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0</v>
@@ -1162,7 +1153,7 @@
         <v>9.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>44.1</v>
@@ -1201,7 +1192,7 @@
         <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>10.8</v>
+        <v>110.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
@@ -1236,10 +1227,10 @@
         <v>23.7</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.9</v>
@@ -1257,10 +1248,10 @@
         <v>18.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>9.1</v>
+        <v>291.3</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
@@ -1275,7 +1266,7 @@
         <v>24.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1323,7 +1314,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1396,7 +1387,7 @@
         <v>22.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.1</v>
+        <v>28.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>17.5</v>
@@ -1417,7 +1408,7 @@
         <v>18.8</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>90.2</v>
@@ -1426,7 +1417,7 @@
         <v>0.4</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1473,7 +1464,7 @@
         <v>26.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>22.7</v>
@@ -1500,7 +1491,7 @@
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1518,7 +1509,7 @@
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>84.2</v>
+        <v>74.2</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3.8</v>
@@ -1533,7 +1524,7 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.5</v>
@@ -1567,7 +1558,7 @@
         <v>11.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.9</v>
@@ -1576,7 +1567,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>22.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1585,7 +1576,7 @@
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>91.2</v>
@@ -1600,10 +1591,10 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>5.8</v>
+        <v>58.2</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>11</v>
@@ -1618,7 +1609,7 @@
         <v>26.4</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>77.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>5.4</v>
@@ -1653,7 +1644,7 @@
         <v>17.9</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>2.7</v>
@@ -1668,7 +1659,7 @@
         <v>18.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>91.2</v>
@@ -1683,7 +1674,7 @@
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>22.7</v>
+        <v>10.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1701,10 +1692,10 @@
         <v>24.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>8.5</v>
+        <v>85.3</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1727,19 +1718,19 @@
         <v>12.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>116.5</v>
+        <v>116.6</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>87.5</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.3</v>
+        <v>17.3</v>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
@@ -1752,16 +1743,16 @@
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>53.2</v>
+        <v>153.2</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>122.2</v>
+        <v>129.2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>112.5</v>
+        <v>182.5</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>126.6</v>
@@ -1770,19 +1761,19 @@
         <v>38.2</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>49.2</v>
+        <v>41.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>114</v>
+        <v>116.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>408.9</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1801,7 +1792,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>20.1</v>
+        <v>0.1</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>28.1</v>
@@ -1822,17 +1813,17 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>2.2</v>
+        <v>22.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>91.2</v>
@@ -1844,7 +1835,7 @@
         <v>25.8</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>25.3</v>
@@ -1862,7 +1853,7 @@
         <v>21.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>82.2</v>
@@ -1897,7 +1888,7 @@
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.1</v>
@@ -1912,10 +1903,10 @@
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.1</v>
+        <v>19.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91.2</v>
@@ -1936,10 +1927,10 @@
         <v>54.2</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>10.1</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>21.8</v>
+        <v>121.8</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -1967,7 +1958,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>30.5</v>
@@ -2000,7 +1991,7 @@
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92.2</v>
@@ -2033,7 +2024,7 @@
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>87.8</v>
+        <v>81.2</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2052,7 +2043,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>28.5</v>
@@ -2064,7 +2055,7 @@
         <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.9</v>
+        <v>29.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2073,7 +2064,7 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -2092,19 +2083,19 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.6</v>
+        <v>26.2</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>23.7</v>
+        <v>29.7</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>72.2</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>22.8</v>
@@ -2113,7 +2104,7 @@
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>85.2</v>
+        <v>25.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2138,7 +2129,7 @@
         <v>1.1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28.3</v>
+        <v>28.9</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2180,13 +2171,13 @@
         <v>19.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>12.1</v>
+        <v>19.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>88.2</v>
+        <v>28.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0.2</v>
@@ -2198,7 +2189,7 @@
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>2.9</v>
+        <v>21.9</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>90.2</v>
@@ -2220,7 +2211,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>29.4</v>
@@ -2253,7 +2244,7 @@
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91.2</v>
@@ -2274,7 +2265,7 @@
         <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>13.9</v>
+        <v>19.9</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24.6</v>
@@ -2306,13 +2297,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>142.5</v>
+        <v>147.6</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.2</v>
+        <v>112.2</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>52.2</v>
@@ -2327,19 +2318,19 @@
         <v>14</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>51.7</v>
+        <v>31.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.1</v>
+        <v>8.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>458.2</v>
+        <v>451.2</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
@@ -2349,13 +2340,13 @@
         <v>107.2</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>11.9</v>
+        <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>36</v>
+        <v>360.2</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>37.7</v>
+        <v>34.7</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>108.4</v>
@@ -2364,10 +2355,10 @@
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>117.7</v>
+        <v>117.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>27.6</v>
+        <v>427.6</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>12.7</v>
@@ -2404,13 +2395,13 @@
         <v>16.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>991999.1</v>
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>18.8</v>
@@ -2431,7 +2422,7 @@
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>2.4</v>
+        <v>21.4</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
@@ -2455,7 +2446,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2478,7 +2469,7 @@
         <v>18.7</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>444.1</v>
@@ -2487,7 +2478,7 @@
         <v>17.1</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>34.4</v>
@@ -2505,7 +2496,7 @@
         <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2532,7 +2523,7 @@
         <v>4.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>67.2</v>
@@ -2555,7 +2546,7 @@
         <v>1.1</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>28.6</v>
+        <v>29.6</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>19.2</v>
@@ -2564,13 +2555,13 @@
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>28.4</v>
+        <v>18.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2582,13 +2573,13 @@
         <v>19.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>9.1</v>
+        <v>91.2</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2597,7 +2588,7 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.3</v>
+        <v>29.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>27.1</v>
@@ -2659,16 +2650,16 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>22.5</v>
+        <v>2.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.8</v>
+        <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>19.1</v>
+        <v>18.2</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>98.2</v>
@@ -2686,7 +2677,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2724,7 +2715,7 @@
         <v>32.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>24.3</v>
@@ -2748,19 +2739,19 @@
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>23.3</v>
@@ -2772,16 +2763,16 @@
         <v>40.2</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>21.1</v>
+        <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>20.2</v>
+        <v>216.2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>14.6</v>
@@ -2847,7 +2838,7 @@
         <v>21.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>72.2</v>
@@ -2868,7 +2859,7 @@
         <v>2.3</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2891,7 +2882,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>118.1</v>
+        <v>119.1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2912,11 +2903,11 @@
         <v>92.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2925,19 +2916,19 @@
         <v>130.7</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>12.9</v>
+        <v>112.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>126.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>222.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>18.2</v>
+        <v>118.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>10.4</v>
+        <v>104.6</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>114.6</v>
@@ -2972,7 +2963,7 @@
         <v>11.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>23.9</v>
+        <v>22.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
@@ -2988,13 +2979,13 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>2.8</v>
+        <v>24</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -3049,7 +3040,7 @@
         <v>1.1</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>38.8</v>
+        <v>32.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>4.5</v>
@@ -3061,13 +3052,13 @@
         <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>22.5</v>
@@ -3077,10 +3068,10 @@
         <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.4</v>
@@ -3101,7 +3092,7 @@
         <v>15.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>25.8</v>
@@ -3136,7 +3127,7 @@
         <v>18</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>94.59999999999999</v>
@@ -3161,7 +3152,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>9</v>
+        <v>90.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3170,16 +3161,16 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>27.8</v>
+        <v>24.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>78.2</v>
+        <v>48.2</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>24.2</v>
+        <v>26.2</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>22</v>
@@ -3188,7 +3179,7 @@
         <v>27.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>2.8</v>
@@ -3210,7 +3201,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>32.1</v>
@@ -3243,7 +3234,7 @@
         <v>1.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>87.2</v>
@@ -3264,7 +3255,7 @@
         <v>67.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20</v>
@@ -3304,7 +3295,7 @@
         <v>18.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>27.4</v>
+        <v>24.4</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>12</v>
@@ -3325,10 +3316,10 @@
         <v>19</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.1</v>
+        <v>28.6</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>92.2</v>
@@ -3346,10 +3337,10 @@
         <v>24.6</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>15.2</v>
+        <v>12.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>22</v>
@@ -3364,7 +3355,7 @@
         <v>13.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>33.2</v>
+        <v>53.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3381,7 +3372,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr"/>
       <c r="D36" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>33.6</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>19</v>
@@ -3390,7 +3381,7 @@
         <v>25.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.5</v>
+        <v>15.6</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>15.4</v>
@@ -3408,10 +3399,10 @@
         <v>18.7</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>90.2</v>
@@ -3429,7 +3420,7 @@
         <v>27.9</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.4</v>
+        <v>44.2</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>28.3</v>
@@ -3491,25 +3482,25 @@
         <v>95.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>2.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>50.2</v>
+        <v>150.4</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.2</v>
+        <v>8.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>142.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>17.5</v>
+        <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>120.4</v>
+        <v>190.4</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>70.3</v>
@@ -3518,7 +3509,7 @@
         <v>124.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>125.9</v>
@@ -3530,7 +3521,7 @@
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>24.7</v>
+        <v>247.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3547,13 +3538,13 @@
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="n">
-        <v>92.3</v>
+        <v>22.3</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3568,16 +3559,16 @@
         <v>4.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>555.5</v>
+        <v>1.1</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>1.5</v>
+        <v>18.6</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>90.90000000000001</v>
@@ -3595,7 +3586,7 @@
         <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
@@ -3610,7 +3601,7 @@
         <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>14.1</v>
@@ -3657,11 +3648,11 @@
         <v>19</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3673,7 +3664,7 @@
         <v>22.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>61.2</v>
@@ -3685,13 +3676,13 @@
         <v>20.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>241.7</v>
+        <v>241</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>22</v>
@@ -3740,10 +3731,10 @@
         <v>18.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1.1</v>
+        <v>29.8</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>92.2</v>
@@ -3752,7 +3743,7 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>21.2</v>
+        <v>31.2</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>28.2</v>
@@ -3764,22 +3755,22 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2.5</v>
+        <v>26.9</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3805,7 +3796,7 @@
         <v>25.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>12.8</v>
+        <v>82.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3854,7 +3845,7 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3887,7 +3878,7 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
@@ -3905,7 +3896,7 @@
         <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3923,16 +3914,16 @@
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4033,7 +4024,7 @@
         <v>122.3</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>34.6</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>102</v>
@@ -4054,10 +4045,10 @@
         <v>7.7</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
@@ -4067,19 +4058,19 @@
         <v>0.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>106.7</v>
+        <v>106.9</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.8</v>
+        <v>241.2</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>95.3</v>
+        <v>96.3</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>85.7</v>
@@ -4088,13 +4079,13 @@
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>232.7</v>
+        <v>327.2</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4111,7 +4102,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr"/>
       <c r="D46" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>32.3</v>
@@ -4132,19 +4123,19 @@
         <v>13.7</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.7</v>
+        <v>9.9</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>14.4</v>
+        <v>12.4</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>2.2</v>
+        <v>22.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>26.7</v>
@@ -4162,7 +4153,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>23.8</v>
+        <v>29.8</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>21.4</v>
@@ -4173,9 +4164,11 @@
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>2.2</v>
+        <v>298.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_decimal_place_correction.xlsx
@@ -761,7 +761,7 @@
         <v>21.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
@@ -770,7 +770,7 @@
         <v>30.6</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>29.8</v>
+        <v>23.8</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>25.3</v>
@@ -835,7 +835,7 @@
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>91.59999999999999</v>
@@ -850,10 +850,10 @@
         <v>21</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>28.1</v>
+        <v>23.1</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>70.2</v>
+        <v>7</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>6.5</v>
@@ -909,7 +909,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>17.4</v>
@@ -918,7 +918,7 @@
         <v>17.5</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>91.2</v>
@@ -951,7 +951,7 @@
         <v>24.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>37.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>4</v>
@@ -1004,7 +1004,7 @@
         <v>2.5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
@@ -1016,7 +1016,7 @@
         <v>19.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>87.2</v>
@@ -1034,7 +1034,7 @@
         <v>24.6</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>74.2</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>23.8</v>
@@ -1075,7 +1075,7 @@
         <v>2.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>18.9</v>
@@ -1177,7 +1177,7 @@
         <v>129.4</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>110.1</v>
+        <v>110.8</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>122.3</v>
@@ -1192,13 +1192,13 @@
         <v>123.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>110.8</v>
+        <v>10.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>382.6</v>
+        <v>382</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>31.1</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.2</v>
@@ -1251,7 +1251,7 @@
         <v>2.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>291.3</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
         <v>8.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>12.3</v>
+        <v>19.3</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.8</v>
@@ -1358,7 +1358,7 @@
         <v>26.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>4.5</v>
@@ -1411,13 +1411,13 @@
         <v>2.8</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>22</v>
@@ -1426,10 +1426,10 @@
         <v>25.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>67.2</v>
+        <v>6.7</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>22.2</v>
@@ -1441,7 +1441,7 @@
         <v>24.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>83.2</v>
@@ -1485,13 +1485,13 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>90.2</v>
@@ -1509,7 +1509,7 @@
         <v>22.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>74.2</v>
+        <v>7.4</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3.8</v>
@@ -1524,7 +1524,7 @@
         <v>22.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>2.5</v>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>29.9</v>
@@ -1567,7 +1567,7 @@
         <v>2.7</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>18.9</v>
@@ -1591,7 +1591,7 @@
         <v>23.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58.2</v>
@@ -1662,7 +1662,7 @@
         <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>91.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.2</v>
@@ -1674,7 +1674,7 @@
         <v>22.9</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>10.7</v>
+        <v>20.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>58.2</v>
@@ -1724,13 +1724,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>81.5</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>17.3</v>
+        <v>14.3</v>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
@@ -1743,13 +1743,13 @@
         <v>1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>153.2</v>
+        <v>35.3</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>129.2</v>
+        <v>10.9</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>182.5</v>
@@ -1764,16 +1764,16 @@
         <v>41.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>116.7</v>
+        <v>11.4</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>124.6</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>408.9</v>
+        <v>708.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>15</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>28.1</v>
@@ -1807,7 +1807,7 @@
         <v>9.6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.9</v>
@@ -1823,7 +1823,7 @@
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.1</v>
+        <v>0.2</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>91.2</v>
@@ -1856,7 +1856,7 @@
         <v>24.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2</v>
@@ -1891,7 +1891,7 @@
         <v>16.6</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.6</v>
@@ -1930,7 +1930,7 @@
         <v>10.1</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>121.8</v>
+        <v>1.8</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>20.8</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>30.5</v>
@@ -1985,16 +1985,16 @@
         <v>27.9</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>18.3</v>
+        <v>19.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>18.2</v>
+        <v>8.5</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.2</v>
@@ -2009,7 +2009,7 @@
         <v>23</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>0.2</v>
@@ -2024,7 +2024,7 @@
         <v>23</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81.2</v>
+        <v>87.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0.6</v>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>28.5</v>
@@ -2055,7 +2055,7 @@
         <v>23.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>29.6</v>
+        <v>9.6</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>17.6</v>
@@ -2064,7 +2064,7 @@
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -2104,7 +2104,7 @@
         <v>20.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>25.3</v>
+        <v>85.3</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>2.6</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>18</v>
@@ -2144,7 +2144,7 @@
         <v>17.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1.9</v>
@@ -2159,7 +2159,7 @@
         <v>18.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>92.2</v>
@@ -2177,7 +2177,7 @@
         <v>22</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>28.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>0.2</v>
@@ -2189,10 +2189,10 @@
         <v>19.1</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.9</v>
+        <v>2.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.8</v>
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>23.2</v>
@@ -2244,7 +2244,7 @@
         <v>18</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>91.2</v>
@@ -2265,7 +2265,7 @@
         <v>56.2</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.9</v>
+        <v>13.9</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24.6</v>
@@ -2274,7 +2274,7 @@
         <v>26.2</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>22.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>80.2</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>147.6</v>
+        <v>147.5</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>90.40000000000001</v>
@@ -2327,26 +2327,26 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>451.2</v>
+        <v>45.7</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
         <v>121</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>107.2</v>
+        <v>107.8</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>119.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>360.2</v>
+        <v>36</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>34.7</v>
+        <v>57.7</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>108.4</v>
@@ -2355,7 +2355,7 @@
         <v>102.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>117.8</v>
+        <v>117.7</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>427.6</v>
@@ -2401,7 +2401,7 @@
         <v>1.8</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>18.8</v>
@@ -2410,10 +2410,10 @@
         <v>18.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>31.2</v>
+        <v>81.2</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.2</v>
@@ -2422,13 +2422,13 @@
         <v>27.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21.4</v>
+        <v>2</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.2</v>
+        <v>78.8</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.9</v>
@@ -2446,7 +2446,7 @@
         <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>18.7</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>444.1</v>
@@ -2493,10 +2493,10 @@
         <v>19.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>92.2</v>
+        <v>0.9</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         <v>23.1</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>67.2</v>
+        <v>67.3</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>19.2</v>
@@ -2555,13 +2555,13 @@
         <v>23.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1.9</v>
@@ -2576,10 +2576,10 @@
         <v>29.6</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>91.2</v>
+        <v>91.8</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
@@ -2588,13 +2588,13 @@
         <v>25.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>27.1</v>
+        <v>0.8</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>76.2</v>
+        <v>7.6</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>5.9</v>
@@ -2606,7 +2606,7 @@
         <v>21.3</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>0.8</v>
@@ -2641,7 +2641,7 @@
         <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>1.9</v>
@@ -2650,7 +2650,7 @@
         <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>18</v>
@@ -2659,16 +2659,16 @@
         <v>18</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>22.1</v>
@@ -2677,7 +2677,7 @@
         <v>23.9</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>0.1</v>
+        <v>6.3</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.9</v>
@@ -2742,13 +2742,13 @@
         <v>16.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>30.1</v>
@@ -2766,16 +2766,16 @@
         <v>12.2</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>216.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>14.6</v>
+        <v>17.6</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>53.2</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr"/>
       <c r="N29" s="3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>90.59999999999999</v>
@@ -2853,7 +2853,7 @@
         <v>21.8</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>2.3</v>
@@ -2882,7 +2882,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>119.1</v>
+        <v>11.8</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>58.8</v>
@@ -2903,11 +2903,11 @@
         <v>92.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>45.1</v>
+        <v>45.7</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
@@ -2928,13 +2928,13 @@
         <v>118.2</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>104.6</v>
+        <v>10.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>114.6</v>
+        <v>117.6</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>372.2</v>
+        <v>382.8</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>32.4</v>
@@ -2960,16 +2960,16 @@
         <v>29.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.1</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.1</v>
@@ -2979,13 +2979,13 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>91.2</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>22.6</v>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>32.8</v>
@@ -3068,7 +3068,7 @@
         <v>18.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>91.2</v>
@@ -3127,10 +3127,10 @@
         <v>18</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>17.9</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>90.3</v>
+        <v>80.3</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0</v>
@@ -3161,19 +3161,19 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>48.2</v>
+        <v>7.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>26.2</v>
+        <v>24.2</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>27.4</v>
@@ -3231,13 +3231,13 @@
         <v>19.7</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>1.2</v>
@@ -3264,7 +3264,7 @@
         <v>21.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>86.3</v>
+        <v>8.6</v>
       </c>
       <c r="Y34" s="3" t="n">
         <v>6.7</v>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>30.4</v>
@@ -3295,10 +3295,10 @@
         <v>18.4</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>24.4</v>
+        <v>27.4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>18.2</v>
@@ -3319,13 +3319,13 @@
         <v>1.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>28</v>
@@ -3340,7 +3340,7 @@
         <v>12.2</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>22</v>
@@ -3390,7 +3390,7 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.5</v>
@@ -3399,13 +3399,13 @@
         <v>18.7</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>90.2</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1</v>
@@ -3435,7 +3435,7 @@
         <v>55.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>17.6</v>
@@ -3458,7 +3458,7 @@
         <v>161.5</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>92.5</v>
+        <v>92.8</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>126.9</v>
@@ -3482,13 +3482,13 @@
         <v>95.09999999999999</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>150.4</v>
+        <v>450</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>8.6</v>
@@ -3500,7 +3500,7 @@
         <v>117.5</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>190.4</v>
+        <v>19</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>70.3</v>
@@ -3521,7 +3521,7 @@
         <v>37.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>247.2</v>
+        <v>24.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>18.4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>13.9</v>
@@ -3559,25 +3559,25 @@
         <v>4.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>28.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.5</v>
@@ -3586,7 +3586,7 @@
         <v>26.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>49.2</v>
+        <v>4.9</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>24.9</v>
@@ -3601,10 +3601,10 @@
         <v>73.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>32.5</v>
@@ -3731,13 +3731,13 @@
         <v>18.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>29.8</v>
+        <v>2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.2</v>
@@ -3755,7 +3755,7 @@
         <v>47.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.8</v>
@@ -3764,13 +3764,13 @@
         <v>25.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>26.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>25.4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>82.8</v>
+        <v>12.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17</v>
@@ -3833,7 +3833,7 @@
         <v>27</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>59.2</v>
+        <v>59.8</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>9</v>
@@ -3845,7 +3845,7 @@
         <v>24.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>82.2</v>
+        <v>82.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>2.6</v>
@@ -3878,7 +3878,7 @@
         <v>25.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>2</v>
@@ -3896,7 +3896,7 @@
         <v>19.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>92.2</v>
@@ -3914,13 +3914,13 @@
         <v>24.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>3.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>0.2</v>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
         <v>122.3</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>34.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>102</v>
@@ -4045,32 +4045,32 @@
         <v>7.7</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>14.6</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>11.1</v>
+        <v>31.1</v>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>26.6</v>
+        <v>266.8</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>106.9</v>
+        <v>106.7</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>102.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>241.2</v>
+        <v>24.1</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>38.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>96.3</v>
+        <v>95.3</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>85.7</v>
@@ -4079,13 +4079,13 @@
         <v>96.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>327.2</v>
+        <v>32.7</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>82.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>17.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>13.7</v>
@@ -4129,16 +4129,16 @@
         <v>12.4</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>92.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>0.2</v>
@@ -4150,7 +4150,7 @@
         <v>22.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>29.8</v>
@@ -4164,9 +4164,7 @@
       <c r="X46" s="3" t="n">
         <v>60.2</v>
       </c>
-      <c r="Y46" s="3" t="n">
-        <v>2.1</v>
-      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="n">
         <v>298.9</v>
       </c>
